--- a/temp_LISTA_S_corregida.xlsx
+++ b/temp_LISTA_S_corregida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edgar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86389290-DA57-49D4-9D7F-09114DA0BB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4F843F-120D-4572-8C46-17C898EBF9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,21 +136,12 @@
     <t>EC600 External Enclosure for 2.5 inch HDD/SSD COLOR BOXBLACK</t>
   </si>
   <si>
-    <t>UR350-128G- RSR/BK</t>
-  </si>
-  <si>
     <t>UR350 USB Flash Drive 128GB USB 3.2 Gen 1 Black (nickel-tone metal finish)</t>
   </si>
   <si>
-    <t>UR350-32G- RSR/BK</t>
-  </si>
-  <si>
     <t>UR350 USB Flash Drive 32GB USB 3.2 Gen 1 Black (nickel-tone metal finish)</t>
   </si>
   <si>
-    <t>UR350-64G- RSR/BK</t>
-  </si>
-  <si>
     <t>UR350 USB Flash Drive 64GB USB 3.2 Gen 1 Black (nickel-tone metal finish)</t>
   </si>
   <si>
@@ -3035,6 +3026,15 @@
   </si>
   <si>
     <t>DELL ECOLOOP - MOCHILA 14" a 16"</t>
+  </si>
+  <si>
+    <t>UR350-128G- RSRBK</t>
+  </si>
+  <si>
+    <t>UR350-64G- RSRBK</t>
+  </si>
+  <si>
+    <t>UR350-32G- RSRBK</t>
   </si>
 </sst>
 </file>
@@ -3153,7 +3153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3188,6 +3188,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3546,7 +3552,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -3566,7 +3572,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -3586,7 +3592,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -3606,7 +3612,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -3626,7 +3632,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4"/>
@@ -3642,7 +3648,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -3662,7 +3668,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3682,7 +3688,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -3702,7 +3708,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3722,7 +3728,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3742,7 +3748,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -3762,7 +3768,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -3782,7 +3788,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -3802,7 +3808,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -3822,11 +3828,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>20</v>
@@ -3842,11 +3848,11 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>39</v>
+      <c r="A23" s="13" t="s">
+        <v>1003</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>20</v>
@@ -3862,11 +3868,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>41</v>
+      <c r="A24" s="13" t="s">
+        <v>1002</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>20</v>
@@ -3882,8 +3888,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>43</v>
+      <c r="A25" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -3898,14 +3904,14 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>44</v>
+      <c r="A26" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D26" s="7">
         <v>33</v>
@@ -3918,14 +3924,14 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>47</v>
+      <c r="A27" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D27" s="7">
         <v>17</v>
@@ -3938,14 +3944,14 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>49</v>
+      <c r="A28" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D28" s="7">
         <v>121</v>
@@ -3958,14 +3964,14 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>51</v>
+      <c r="A29" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D29" s="7">
         <v>34</v>
@@ -3978,14 +3984,14 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>53</v>
+      <c r="A30" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D30" s="7">
         <v>57</v>
@@ -3998,8 +4004,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>55</v>
+      <c r="A31" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -4014,14 +4020,14 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>56</v>
+      <c r="A32" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D32" s="7">
         <v>100</v>
@@ -4034,14 +4040,14 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>59</v>
+      <c r="A33" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D33" s="7">
         <v>100</v>
@@ -4054,8 +4060,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>61</v>
+      <c r="A34" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -4070,14 +4076,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>62</v>
+      <c r="A35" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D35" s="7">
         <v>46</v>
@@ -4090,14 +4096,14 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>65</v>
+      <c r="A36" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D36" s="7">
         <v>95</v>
@@ -4110,14 +4116,14 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>67</v>
+      <c r="A37" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D37" s="7">
         <v>27</v>
@@ -4130,8 +4136,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>69</v>
+      <c r="A38" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -4146,14 +4152,14 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>70</v>
+      <c r="A39" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D39" s="7">
         <v>76</v>
@@ -4166,14 +4172,14 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>73</v>
+      <c r="A40" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D40" s="7">
         <v>24</v>
@@ -4186,8 +4192,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>75</v>
+      <c r="A41" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -4202,14 +4208,14 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>76</v>
+      <c r="A42" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D42" s="7">
         <v>12</v>
@@ -4222,14 +4228,14 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>79</v>
+      <c r="A43" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D43" s="7">
         <v>83</v>
@@ -4242,14 +4248,14 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>81</v>
+      <c r="A44" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D44" s="7">
         <v>20</v>
@@ -4262,14 +4268,14 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>83</v>
+      <c r="A45" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D45" s="7">
         <v>18</v>
@@ -4282,14 +4288,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>85</v>
+      <c r="A46" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D46" s="7">
         <v>18</v>
@@ -4302,14 +4308,14 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>87</v>
+      <c r="A47" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D47" s="7">
         <v>555</v>
@@ -4322,14 +4328,14 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>89</v>
+      <c r="A48" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D48" s="7">
         <v>30</v>
@@ -4342,14 +4348,14 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>91</v>
+      <c r="A49" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D49" s="7">
         <v>12</v>
@@ -4362,14 +4368,14 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>93</v>
+      <c r="A50" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D50" s="7">
         <v>11</v>
@@ -4382,14 +4388,14 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>95</v>
+      <c r="A51" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D51" s="7">
         <v>87</v>
@@ -4402,14 +4408,14 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>97</v>
+      <c r="A52" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D52" s="7">
         <v>106</v>
@@ -4422,14 +4428,14 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>99</v>
+      <c r="A53" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D53" s="7">
         <v>119</v>
@@ -4442,14 +4448,14 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>101</v>
+      <c r="A54" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D54" s="7">
         <v>101</v>
@@ -4462,14 +4468,14 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>103</v>
+      <c r="A55" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D55" s="7">
         <v>94</v>
@@ -4482,14 +4488,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>105</v>
+      <c r="A56" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D56" s="7">
         <v>221</v>
@@ -4502,14 +4508,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>107</v>
+      <c r="A57" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D57" s="7">
         <v>234</v>
@@ -4522,14 +4528,14 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>109</v>
+      <c r="A58" s="13" t="s">
+        <v>106</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D58" s="7">
         <v>232</v>
@@ -4542,14 +4548,14 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>111</v>
+      <c r="A59" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D59" s="7">
         <v>95</v>
@@ -4562,14 +4568,14 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>113</v>
+      <c r="A60" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D60" s="7">
         <v>56</v>
@@ -4582,14 +4588,14 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>115</v>
+      <c r="A61" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D61" s="7">
         <v>32</v>
@@ -4602,14 +4608,14 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>117</v>
+      <c r="A62" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D62" s="7">
         <v>32</v>
@@ -4622,14 +4628,14 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>119</v>
+      <c r="A63" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D63" s="7">
         <v>137</v>
@@ -4642,14 +4648,14 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>121</v>
+      <c r="A64" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D64" s="7">
         <v>135</v>
@@ -4662,14 +4668,14 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>123</v>
+      <c r="A65" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D65" s="7">
         <v>142</v>
@@ -4682,14 +4688,14 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>125</v>
+      <c r="A66" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D66" s="7">
         <v>37</v>
@@ -4702,14 +4708,14 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>127</v>
+      <c r="A67" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D67" s="7">
         <v>89</v>
@@ -4722,14 +4728,14 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>129</v>
+      <c r="A68" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D68" s="7">
         <v>36</v>
@@ -4742,14 +4748,14 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>131</v>
+      <c r="A69" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D69" s="7">
         <v>78</v>
@@ -4762,14 +4768,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>133</v>
+      <c r="A70" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D70" s="7">
         <v>37</v>
@@ -4782,14 +4788,14 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>135</v>
+      <c r="A71" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D71" s="7">
         <v>97</v>
@@ -4802,14 +4808,14 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>137</v>
+      <c r="A72" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D72" s="7">
         <v>11</v>
@@ -4822,14 +4828,14 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>139</v>
+      <c r="A73" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D73" s="7">
         <v>84</v>
@@ -4842,14 +4848,14 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>141</v>
+      <c r="A74" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D74" s="7">
         <v>55</v>
@@ -4862,14 +4868,14 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>143</v>
+      <c r="A75" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D75" s="7">
         <v>34</v>
@@ -4882,14 +4888,14 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>145</v>
+      <c r="A76" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D76" s="7">
         <v>147</v>
@@ -4902,14 +4908,14 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>147</v>
+      <c r="A77" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D77" s="7">
         <v>65</v>
@@ -4922,14 +4928,14 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>149</v>
+      <c r="A78" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D78" s="7">
         <v>47</v>
@@ -4942,14 +4948,14 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>151</v>
+      <c r="A79" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D79" s="7">
         <v>41</v>
@@ -4962,14 +4968,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>153</v>
+      <c r="A80" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D80" s="7">
         <v>49</v>
@@ -4982,14 +4988,14 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>155</v>
+      <c r="A81" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D81" s="7">
         <v>20</v>
@@ -5002,14 +5008,14 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>157</v>
+      <c r="A82" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D82" s="7">
         <v>18</v>
@@ -5022,14 +5028,14 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>159</v>
+      <c r="A83" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D83" s="7">
         <v>40</v>
@@ -5042,14 +5048,14 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>161</v>
+      <c r="A84" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D84" s="7">
         <v>39</v>
@@ -5062,14 +5068,14 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>163</v>
+      <c r="A85" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D85" s="7">
         <v>39</v>
@@ -5082,14 +5088,14 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>165</v>
+      <c r="A86" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D86" s="7">
         <v>39</v>
@@ -5102,14 +5108,14 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>167</v>
+      <c r="A87" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D87" s="7">
         <v>29</v>
@@ -5122,14 +5128,14 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>169</v>
+      <c r="A88" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D88" s="7">
         <v>29</v>
@@ -5142,14 +5148,14 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
-        <v>171</v>
+      <c r="A89" s="13" t="s">
+        <v>168</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D89" s="7">
         <v>29</v>
@@ -5162,14 +5168,14 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>173</v>
+      <c r="A90" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D90" s="7">
         <v>29</v>
@@ -5183,7 +5189,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -5199,13 +5205,13 @@
     </row>
     <row r="92" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D92" s="7">
         <v>18</v>
@@ -5219,13 +5225,13 @@
     </row>
     <row r="93" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D93" s="7">
         <v>16</v>
@@ -5239,7 +5245,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -5255,13 +5261,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D95" s="7">
         <v>15</v>
@@ -5275,7 +5281,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -5291,13 +5297,13 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D97" s="7">
         <v>12</v>
@@ -5311,7 +5317,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -5327,13 +5333,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D99" s="7">
         <v>127</v>
@@ -5347,7 +5353,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -5363,13 +5369,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D101" s="7">
         <v>14</v>
@@ -5383,13 +5389,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D102" s="7">
         <v>153</v>
@@ -5403,13 +5409,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D103" s="7">
         <v>122</v>
@@ -5423,13 +5429,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D104" s="7">
         <v>101</v>
@@ -5443,13 +5449,13 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D105" s="7">
         <v>48</v>
@@ -5463,13 +5469,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D106" s="7">
         <v>44</v>
@@ -5483,13 +5489,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D107" s="7">
         <v>258</v>
@@ -5503,13 +5509,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D108" s="7">
         <v>136</v>
@@ -5523,13 +5529,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D109" s="7">
         <v>69</v>
@@ -5543,13 +5549,13 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D110" s="7">
         <v>65</v>
@@ -5562,14 +5568,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
-        <v>215</v>
+      <c r="A111" s="13" t="s">
+        <v>212</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D111" s="7">
         <v>70</v>
@@ -5583,13 +5589,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D112" s="7">
         <v>26</v>
@@ -5603,13 +5609,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D113" s="7">
         <v>17</v>
@@ -5623,13 +5629,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D114" s="7">
         <v>56</v>
@@ -5642,14 +5648,14 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
-        <v>223</v>
+      <c r="A115" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D115" s="7">
         <v>81</v>
@@ -5663,13 +5669,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D116" s="7">
         <v>56</v>
@@ -5683,13 +5689,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D117" s="7">
         <v>209</v>
@@ -5703,13 +5709,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D118" s="7">
         <v>23</v>
@@ -5723,13 +5729,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D119" s="7">
         <v>199</v>
@@ -5743,13 +5749,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D120" s="7">
         <v>79</v>
@@ -5763,13 +5769,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D121" s="7">
         <v>147</v>
@@ -5783,13 +5789,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D122" s="7">
         <v>715</v>
@@ -5803,13 +5809,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D123" s="7">
         <v>30</v>
@@ -5823,7 +5829,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5839,13 +5845,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D125" s="7">
         <v>19</v>
@@ -5859,7 +5865,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -5875,13 +5881,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D127" s="7">
         <v>23</v>
@@ -5895,13 +5901,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D128" s="7">
         <v>154</v>
@@ -5915,13 +5921,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D129" s="7">
         <v>112</v>
@@ -5935,13 +5941,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D130" s="7">
         <v>60</v>
@@ -5955,13 +5961,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D131" s="7">
         <v>55</v>
@@ -5975,13 +5981,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D132" s="7">
         <v>116</v>
@@ -5995,13 +6001,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D133" s="7">
         <v>66</v>
@@ -6015,13 +6021,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D134" s="7">
         <v>15</v>
@@ -6035,13 +6041,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D135" s="7">
         <v>22</v>
@@ -6055,13 +6061,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D136" s="7">
         <v>12</v>
@@ -6075,13 +6081,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D137" s="7">
         <v>12</v>
@@ -6095,13 +6101,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D138" s="7">
         <v>11</v>
@@ -6115,13 +6121,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D139" s="7">
         <v>22</v>
@@ -6135,13 +6141,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D140" s="7">
         <v>23</v>
@@ -6155,13 +6161,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D141" s="7">
         <v>23</v>
@@ -6175,13 +6181,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D142" s="7">
         <v>101</v>
@@ -6195,13 +6201,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D143" s="7">
         <v>82</v>
@@ -6215,13 +6221,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D144" s="7">
         <v>132</v>
@@ -6235,13 +6241,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D145" s="7">
         <v>1118</v>
@@ -6255,13 +6261,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D146" s="7">
         <v>936</v>
@@ -6275,13 +6281,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D147" s="7">
         <v>892</v>
@@ -6295,13 +6301,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D148" s="7">
         <v>934</v>
@@ -6315,13 +6321,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D149" s="7">
         <v>60</v>
@@ -6335,13 +6341,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D150" s="7">
         <v>70</v>
@@ -6355,7 +6361,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -6371,13 +6377,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D152" s="7">
         <v>84</v>
@@ -6391,7 +6397,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -6407,13 +6413,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D154" s="7">
         <v>50</v>
@@ -6427,13 +6433,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D155" s="7">
         <v>11</v>
@@ -6447,13 +6453,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D156" s="7">
         <v>65</v>
@@ -6467,13 +6473,13 @@
     </row>
     <row r="157" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D157" s="7">
         <v>16</v>
@@ -6487,13 +6493,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D158" s="7">
         <v>116</v>
@@ -6507,13 +6513,13 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D159" s="7">
         <v>154</v>
@@ -6527,13 +6533,13 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D160" s="7">
         <v>58</v>
@@ -6547,13 +6553,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D161" s="7">
         <v>156</v>
@@ -6567,7 +6573,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6583,13 +6589,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D163" s="7">
         <v>15</v>
@@ -6603,13 +6609,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D164" s="7">
         <v>22</v>
@@ -6623,13 +6629,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D165" s="7">
         <v>19</v>
@@ -6643,13 +6649,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D166" s="7">
         <v>30</v>
@@ -6663,13 +6669,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D167" s="7">
         <v>33</v>
@@ -6683,13 +6689,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D168" s="7">
         <v>43</v>
@@ -6703,13 +6709,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D169" s="7">
         <v>19</v>
@@ -6723,13 +6729,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D170" s="7">
         <v>18</v>
@@ -6743,13 +6749,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D171" s="7">
         <v>212</v>
@@ -6763,13 +6769,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D172" s="7">
         <v>52</v>
@@ -6783,13 +6789,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D173" s="7">
         <v>17</v>
@@ -6803,13 +6809,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D174" s="7">
         <v>47</v>
@@ -6823,13 +6829,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D175" s="7">
         <v>38</v>
@@ -6843,13 +6849,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D176" s="7">
         <v>38</v>
@@ -6863,13 +6869,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D177" s="7">
         <v>13</v>
@@ -6883,13 +6889,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D178" s="7">
         <v>14</v>
@@ -6903,13 +6909,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D179" s="7">
         <v>19</v>
@@ -6923,13 +6929,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D180" s="7">
         <v>53</v>
@@ -6943,13 +6949,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D181" s="7">
         <v>37</v>
@@ -6963,13 +6969,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D182" s="7">
         <v>11</v>
@@ -6983,13 +6989,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D183" s="7">
         <v>29</v>
@@ -7003,13 +7009,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D184" s="7">
         <v>47</v>
@@ -7023,13 +7029,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D185" s="7">
         <v>542</v>
@@ -7043,13 +7049,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D186" s="7">
         <v>284</v>
@@ -7063,13 +7069,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D187" s="7">
         <v>180</v>
@@ -7083,13 +7089,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D188" s="7">
         <v>34</v>
@@ -7103,13 +7109,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D189" s="7">
         <v>168</v>
@@ -7123,13 +7129,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D190" s="7">
         <v>34</v>
@@ -7143,13 +7149,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D191" s="7">
         <v>26</v>
@@ -7163,13 +7169,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D192" s="7">
         <v>14</v>
@@ -7183,13 +7189,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D193" s="7">
         <v>50</v>
@@ -7203,13 +7209,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D194" s="7">
         <v>128</v>
@@ -7223,13 +7229,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D195" s="7">
         <v>24</v>
@@ -7243,13 +7249,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D196" s="7">
         <v>44</v>
@@ -7263,13 +7269,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D197" s="7">
         <v>26</v>
@@ -7283,13 +7289,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D198" s="7">
         <v>29</v>
@@ -7303,13 +7309,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D199" s="7">
         <v>34</v>
@@ -7323,13 +7329,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D200" s="7">
         <v>44</v>
@@ -7343,13 +7349,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D201" s="7">
         <v>32</v>
@@ -7363,13 +7369,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D202" s="7">
         <v>33</v>
@@ -7383,13 +7389,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D203" s="7">
         <v>49</v>
@@ -7403,13 +7409,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D204" s="7">
         <v>18</v>
@@ -7423,13 +7429,13 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D205" s="7">
         <v>15</v>
@@ -7443,13 +7449,13 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D206" s="7">
         <v>17</v>
@@ -7463,13 +7469,13 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D207" s="7">
         <v>22</v>
@@ -7483,13 +7489,13 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D208" s="7">
         <v>36</v>
@@ -7503,7 +7509,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -7519,13 +7525,13 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D210" s="7">
         <v>12</v>
@@ -7539,13 +7545,13 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D211" s="7">
         <v>21</v>
@@ -7559,13 +7565,13 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D212" s="7">
         <v>193</v>
@@ -7579,13 +7585,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D213" s="7">
         <v>38</v>
@@ -7599,13 +7605,13 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D214" s="7">
         <v>197</v>
@@ -7619,13 +7625,13 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D215" s="7">
         <v>38</v>
@@ -7639,13 +7645,13 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D216" s="7">
         <v>374</v>
@@ -7659,13 +7665,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D217" s="7">
         <v>80</v>
@@ -7679,13 +7685,13 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D218" s="7">
         <v>92</v>
@@ -7699,13 +7705,13 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D219" s="7">
         <v>65</v>
@@ -7719,7 +7725,7 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7735,13 +7741,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D221" s="7">
         <v>21</v>
@@ -7755,13 +7761,13 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D222" s="7">
         <v>275</v>
@@ -7775,13 +7781,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D223" s="7">
         <v>158</v>
@@ -7795,13 +7801,13 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D224" s="7">
         <v>828</v>
@@ -7815,13 +7821,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D225" s="7">
         <v>191</v>
@@ -7835,13 +7841,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D226" s="7">
         <v>140</v>
@@ -7855,13 +7861,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D227" s="7">
         <v>125</v>
@@ -7875,13 +7881,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D228" s="7">
         <v>125</v>
@@ -7895,13 +7901,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D229" s="7">
         <v>37</v>
@@ -7915,13 +7921,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D230" s="7">
         <v>342</v>
@@ -7935,13 +7941,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D231" s="7">
         <v>11</v>
@@ -7955,13 +7961,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D232" s="7">
         <v>15</v>
@@ -7975,13 +7981,13 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D233" s="7">
         <v>18</v>
@@ -7995,13 +8001,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D234" s="7">
         <v>72</v>
@@ -8015,13 +8021,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D235" s="7">
         <v>69</v>
@@ -8035,13 +8041,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D236" s="7">
         <v>172</v>
@@ -8055,13 +8061,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D237" s="7">
         <v>589</v>
@@ -8075,13 +8081,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D238" s="7">
         <v>96</v>
@@ -8095,13 +8101,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D239" s="7">
         <v>172</v>
@@ -8115,13 +8121,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D240" s="7">
         <v>721</v>
@@ -8135,13 +8141,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D241" s="7">
         <v>96</v>
@@ -8155,13 +8161,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D242" s="7">
         <v>172</v>
@@ -8175,13 +8181,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D243" s="7">
         <v>134</v>
@@ -8195,13 +8201,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D244" s="7">
         <v>667</v>
@@ -8215,13 +8221,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D245" s="7">
         <v>202</v>
@@ -8235,13 +8241,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D246" s="7">
         <v>64</v>
@@ -8255,13 +8261,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D247" s="7">
         <v>92</v>
@@ -8275,7 +8281,7 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -8291,13 +8297,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D249" s="7">
         <v>596</v>
@@ -8311,13 +8317,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D250" s="7">
         <v>517</v>
@@ -8331,13 +8337,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D251" s="7">
         <v>296</v>
@@ -8351,13 +8357,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D252" s="7">
         <v>897</v>
@@ -8371,13 +8377,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D253" s="7">
         <v>264</v>
@@ -8391,13 +8397,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D254" s="7">
         <v>613</v>
@@ -8411,13 +8417,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D255" s="7">
         <v>100</v>
@@ -8431,13 +8437,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D256" s="7">
         <v>33</v>
@@ -8451,13 +8457,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D257" s="7">
         <v>11</v>
@@ -8471,13 +8477,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D258" s="7">
         <v>37</v>
@@ -8491,13 +8497,13 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D259" s="7">
         <v>238</v>
@@ -8511,13 +8517,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D260" s="7">
         <v>195</v>
@@ -8531,7 +8537,7 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8547,13 +8553,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D262" s="7">
         <v>19</v>
@@ -8567,13 +8573,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D263" s="7">
         <v>20</v>
@@ -8587,13 +8593,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D264" s="7">
         <v>26</v>
@@ -8607,13 +8613,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D265" s="7">
         <v>11</v>
@@ -8627,13 +8633,13 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D266" s="7">
         <v>20</v>
@@ -8647,13 +8653,13 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D267" s="7">
         <v>21</v>
@@ -8667,13 +8673,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D268" s="7">
         <v>18</v>
@@ -8687,13 +8693,13 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D269" s="7">
         <v>25</v>
@@ -8707,13 +8713,13 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D270" s="7">
         <v>40</v>
@@ -8727,13 +8733,13 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D271" s="7">
         <v>14</v>
@@ -8747,13 +8753,13 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D272" s="7">
         <v>13</v>
@@ -8767,13 +8773,13 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D273" s="7">
         <v>15</v>
@@ -8787,13 +8793,13 @@
     </row>
     <row r="274" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D274" s="7">
         <v>20</v>
@@ -8807,13 +8813,13 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D275" s="7">
         <v>23</v>
@@ -8827,13 +8833,13 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D276" s="7">
         <v>31</v>
@@ -8847,7 +8853,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -8863,13 +8869,13 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D278" s="7">
         <v>56</v>
@@ -8883,13 +8889,13 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D279" s="7">
         <v>48</v>
@@ -8903,13 +8909,13 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D280" s="7">
         <v>19</v>
@@ -8923,7 +8929,7 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -8939,13 +8945,13 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D282" s="7">
         <v>26</v>
@@ -8959,13 +8965,13 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D283" s="7">
         <v>32</v>
@@ -8979,13 +8985,13 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D284" s="7">
         <v>58</v>
@@ -8999,7 +9005,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -9015,13 +9021,13 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D286" s="7">
         <v>19</v>
@@ -9035,13 +9041,13 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D287" s="7">
         <v>95</v>
@@ -9055,13 +9061,13 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D288" s="7">
         <v>86</v>
@@ -9075,13 +9081,13 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D289" s="7">
         <v>50</v>
@@ -9095,13 +9101,13 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D290" s="7">
         <v>22</v>
@@ -9115,13 +9121,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D291" s="7">
         <v>20</v>
@@ -9135,13 +9141,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D292" s="7">
         <v>15</v>
@@ -9155,13 +9161,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D293" s="7">
         <v>261</v>
@@ -9175,13 +9181,13 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D294" s="7">
         <v>24</v>
@@ -9195,13 +9201,13 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D295" s="7">
         <v>20</v>
@@ -9215,13 +9221,13 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D296" s="7">
         <v>198</v>
@@ -9235,13 +9241,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D297" s="7">
         <v>237</v>
@@ -9255,13 +9261,13 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D298" s="7">
         <v>287</v>
@@ -9275,13 +9281,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D299" s="7">
         <v>292</v>
@@ -9295,13 +9301,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="6" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D300" s="7">
         <v>15</v>
@@ -9315,13 +9321,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="6" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D301" s="7">
         <v>24</v>
@@ -9335,13 +9341,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D302" s="7">
         <v>69</v>
@@ -9355,13 +9361,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="6" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D303" s="7">
         <v>20</v>
@@ -9375,13 +9381,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D304" s="7">
         <v>22</v>
@@ -9395,13 +9401,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D305" s="7">
         <v>37</v>
@@ -9415,13 +9421,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D306" s="7">
         <v>95</v>
@@ -9435,13 +9441,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D307" s="7">
         <v>43</v>
@@ -9455,13 +9461,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D308" s="7">
         <v>333</v>
@@ -9475,13 +9481,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="6" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D309" s="7">
         <v>126</v>
@@ -9495,13 +9501,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D310" s="7">
         <v>84</v>
@@ -9515,13 +9521,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D311" s="7">
         <v>100</v>
@@ -9535,13 +9541,13 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D312" s="7">
         <v>34</v>
@@ -9555,13 +9561,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D313" s="7">
         <v>78</v>
@@ -9575,13 +9581,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D314" s="7">
         <v>172</v>
@@ -9595,13 +9601,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D315" s="7">
         <v>48</v>
@@ -9615,13 +9621,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D316" s="7">
         <v>45</v>
@@ -9635,13 +9641,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D317" s="7">
         <v>20</v>
@@ -9655,13 +9661,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D318" s="7">
         <v>28</v>
@@ -9675,13 +9681,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D319" s="7">
         <v>122</v>
@@ -9695,13 +9701,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D320" s="7">
         <v>50</v>
@@ -9715,13 +9721,13 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D321" s="7">
         <v>69</v>
@@ -9735,13 +9741,13 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D322" s="7">
         <v>15</v>
@@ -9755,13 +9761,13 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D323" s="7">
         <v>52</v>
@@ -9775,13 +9781,13 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D324" s="7">
         <v>14</v>
@@ -9795,13 +9801,13 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D325" s="7">
         <v>20</v>
@@ -9815,13 +9821,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D326" s="7">
         <v>15</v>
@@ -9835,13 +9841,13 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D327" s="7">
         <v>18</v>
@@ -9855,13 +9861,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D328" s="7">
         <v>17</v>
@@ -9875,13 +9881,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D329" s="7">
         <v>15</v>
@@ -9895,13 +9901,13 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D330" s="7">
         <v>20</v>
@@ -9915,13 +9921,13 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D331" s="7">
         <v>56</v>
@@ -9935,13 +9941,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D332" s="7">
         <v>40</v>
@@ -9955,13 +9961,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D333" s="7">
         <v>16</v>
@@ -9975,13 +9981,13 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D334" s="7">
         <v>198</v>
@@ -9995,13 +10001,13 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D335" s="7">
         <v>159</v>
@@ -10015,13 +10021,13 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D336" s="7">
         <v>15</v>
@@ -10035,13 +10041,13 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D337" s="7">
         <v>16</v>
@@ -10055,13 +10061,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D338" s="7">
         <v>35</v>
@@ -10075,13 +10081,13 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D339" s="7">
         <v>31</v>
@@ -10095,13 +10101,13 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D340" s="7">
         <v>31</v>
@@ -10115,13 +10121,13 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D341" s="7">
         <v>30</v>
@@ -10135,13 +10141,13 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D342" s="7">
         <v>19</v>
@@ -10155,13 +10161,13 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D343" s="7">
         <v>23</v>
@@ -10175,13 +10181,13 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D344" s="7">
         <v>30</v>
@@ -10195,13 +10201,13 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D345" s="7">
         <v>40</v>
@@ -10215,13 +10221,13 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D346" s="7">
         <v>16</v>
@@ -10235,13 +10241,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D347" s="7">
         <v>30</v>
@@ -10255,13 +10261,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D348" s="7">
         <v>15</v>
@@ -10275,13 +10281,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D349" s="7">
         <v>20</v>
@@ -10295,13 +10301,13 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D350" s="7">
         <v>16</v>
@@ -10315,13 +10321,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D351" s="7">
         <v>143</v>
@@ -10335,13 +10341,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D352" s="7">
         <v>198</v>
@@ -10355,13 +10361,13 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D353" s="7">
         <v>46</v>
@@ -10375,13 +10381,13 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D354" s="7">
         <v>58</v>
@@ -10395,13 +10401,13 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="6" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D355" s="7">
         <v>21</v>
@@ -10415,13 +10421,13 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="6" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D356" s="7">
         <v>11</v>
@@ -10435,7 +10441,7 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -10451,13 +10457,13 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D358" s="7">
         <v>20</v>
@@ -10471,7 +10477,7 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -10487,13 +10493,13 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D360" s="7">
         <v>967</v>
@@ -10507,7 +10513,7 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -10523,13 +10529,13 @@
     </row>
     <row r="362" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D362" s="7">
         <v>46</v>
@@ -10543,13 +10549,13 @@
     </row>
     <row r="363" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D363" s="7">
         <v>18</v>
@@ -10563,13 +10569,13 @@
     </row>
     <row r="364" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D364" s="7">
         <v>20</v>
@@ -10583,13 +10589,13 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="6" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D365" s="7">
         <v>150</v>
@@ -10603,13 +10609,13 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D366" s="7">
         <v>86</v>
@@ -10623,13 +10629,13 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D367" s="7">
         <v>23</v>
@@ -10643,13 +10649,13 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D368" s="7">
         <v>29</v>
@@ -10663,13 +10669,13 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D369" s="7">
         <v>23</v>
@@ -10683,7 +10689,7 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -10699,13 +10705,13 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D371" s="7">
         <v>57</v>
@@ -10719,13 +10725,13 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D372" s="7">
         <v>15</v>
@@ -10739,13 +10745,13 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D373" s="7">
         <v>30</v>
@@ -10759,13 +10765,13 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D374" s="7">
         <v>29</v>
@@ -10779,13 +10785,13 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D375" s="7">
         <v>15</v>
@@ -10799,13 +10805,13 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D376" s="7">
         <v>40</v>
@@ -10819,13 +10825,13 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D377" s="7">
         <v>40</v>
@@ -10839,13 +10845,13 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D378" s="7">
         <v>50</v>
@@ -10859,13 +10865,13 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D379" s="7">
         <v>15</v>
@@ -10879,13 +10885,13 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D380" s="7">
         <v>35</v>
@@ -10899,13 +10905,13 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="6" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D381" s="7">
         <v>15</v>
@@ -10919,13 +10925,13 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="6" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D382" s="7">
         <v>35</v>
@@ -10939,13 +10945,13 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="6" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D383" s="7">
         <v>21</v>
@@ -10959,13 +10965,13 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="6" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D384" s="7">
         <v>34</v>
@@ -10979,13 +10985,13 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D385" s="7">
         <v>16</v>
@@ -10999,13 +11005,13 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="6" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D386" s="7">
         <v>24</v>
@@ -11019,13 +11025,13 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="6" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D387" s="7">
         <v>44</v>
@@ -11039,13 +11045,13 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="6" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D388" s="7">
         <v>30</v>
@@ -11059,13 +11065,13 @@
     </row>
     <row r="389" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D389" s="7">
         <v>194</v>
@@ -11079,13 +11085,13 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="6" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D390" s="7">
         <v>46</v>
@@ -11099,13 +11105,13 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="6" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D391" s="7">
         <v>33</v>
@@ -11119,13 +11125,13 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="6" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D392" s="7">
         <v>17</v>
@@ -11139,13 +11145,13 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="6" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D393" s="7">
         <v>35</v>
@@ -11159,13 +11165,13 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="6" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D394" s="7">
         <v>16</v>
@@ -11179,13 +11185,13 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D395" s="7">
         <v>26</v>
@@ -11199,13 +11205,13 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D396" s="7">
         <v>19</v>
@@ -11219,13 +11225,13 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D397" s="7">
         <v>46</v>
@@ -11239,13 +11245,13 @@
     </row>
     <row r="398" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D398" s="7">
         <v>23</v>
@@ -11259,13 +11265,13 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D399" s="7">
         <v>13</v>
@@ -11279,7 +11285,7 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -11295,13 +11301,13 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D401" s="7">
         <v>40</v>
@@ -11315,13 +11321,13 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D402" s="7">
         <v>42</v>
@@ -11335,13 +11341,13 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D403" s="7">
         <v>13</v>
@@ -11355,13 +11361,13 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D404" s="7">
         <v>21</v>
@@ -11375,13 +11381,13 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D405" s="7">
         <v>14</v>
@@ -11395,7 +11401,7 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -11411,13 +11417,13 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D407" s="7">
         <v>13</v>
@@ -11431,13 +11437,13 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D408" s="7">
         <v>20</v>
@@ -11451,13 +11457,13 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D409" s="7">
         <v>23</v>
@@ -11471,13 +11477,13 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D410" s="7">
         <v>24</v>
@@ -11491,13 +11497,13 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D411" s="7">
         <v>13</v>
@@ -11511,13 +11517,13 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D412" s="7">
         <v>14</v>
@@ -11531,13 +11537,13 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D413" s="7">
         <v>28</v>
@@ -11551,13 +11557,13 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D414" s="7">
         <v>12</v>
@@ -11571,13 +11577,13 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D415" s="7">
         <v>22</v>
@@ -11591,13 +11597,13 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D416" s="7">
         <v>52</v>
@@ -11611,13 +11617,13 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="6" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D417" s="7">
         <v>27</v>
@@ -11631,13 +11637,13 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="6" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D418" s="7">
         <v>34</v>
@@ -11651,13 +11657,13 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D419" s="7">
         <v>18</v>
@@ -11671,7 +11677,7 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -11687,13 +11693,13 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D421" s="7">
         <v>159</v>
@@ -11707,7 +11713,7 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -11723,13 +11729,13 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D423" s="7">
         <v>38</v>
@@ -11743,13 +11749,13 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D424" s="7">
         <v>17</v>
@@ -11763,7 +11769,7 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -11779,13 +11785,13 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D426" s="7">
         <v>15</v>
@@ -11799,13 +11805,13 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D427" s="7">
         <v>30</v>
@@ -11819,13 +11825,13 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D428" s="7">
         <v>18</v>
@@ -11839,13 +11845,13 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D429" s="7">
         <v>31</v>
@@ -11859,13 +11865,13 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D430" s="7">
         <v>20</v>
@@ -11879,13 +11885,13 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D431" s="7">
         <v>11</v>
@@ -11899,13 +11905,13 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D432" s="7">
         <v>20</v>
@@ -11919,13 +11925,13 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="6" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D433" s="7">
         <v>15</v>
@@ -11939,13 +11945,13 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="6" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D434" s="7">
         <v>23</v>
@@ -11959,13 +11965,13 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="6" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D435" s="7">
         <v>18</v>
@@ -11979,13 +11985,13 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="6" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D436" s="7">
         <v>42</v>
@@ -11999,13 +12005,13 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="6" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D437" s="7">
         <v>80</v>
@@ -12019,13 +12025,13 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D438" s="7">
         <v>76</v>
@@ -12039,13 +12045,13 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D439" s="7">
         <v>107</v>
@@ -12059,13 +12065,13 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D440" s="7">
         <v>35</v>
@@ -12079,13 +12085,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D441" s="7">
         <v>25</v>
@@ -12099,13 +12105,13 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D442" s="7">
         <v>31</v>
@@ -12119,13 +12125,13 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D443" s="7">
         <v>22</v>
@@ -12139,13 +12145,13 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D444" s="7">
         <v>15</v>
@@ -12159,13 +12165,13 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B445" s="6" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D445" s="7">
         <v>36</v>
@@ -12179,13 +12185,13 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B446" s="6" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D446" s="7">
         <v>15</v>
@@ -12199,13 +12205,13 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D447" s="7">
         <v>12</v>
@@ -12219,13 +12225,13 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B448" s="6" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D448" s="7">
         <v>12</v>
@@ -12239,13 +12245,13 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D449" s="7">
         <v>15</v>
@@ -12259,13 +12265,13 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B450" s="6" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D450" s="7">
         <v>406</v>
@@ -12279,13 +12285,13 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D451" s="7">
         <v>311</v>
@@ -12299,13 +12305,13 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D452" s="7">
         <v>20</v>
@@ -12319,13 +12325,13 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D453" s="7">
         <v>14</v>
@@ -12339,7 +12345,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -12355,13 +12361,13 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="6" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D455" s="7">
         <v>19</v>
@@ -12375,7 +12381,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -12391,13 +12397,13 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D457" s="7">
         <v>43</v>
@@ -12411,13 +12417,13 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D458" s="7">
         <v>57</v>
@@ -12431,7 +12437,7 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -12447,13 +12453,13 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D460" s="7">
         <v>19</v>
@@ -12467,13 +12473,13 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D461" s="7">
         <v>100</v>
@@ -12487,13 +12493,13 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D462" s="7">
         <v>200</v>
@@ -12507,13 +12513,13 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B463" s="6" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C463" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D463" s="7">
         <v>32</v>
@@ -12527,13 +12533,13 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B464" s="6" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C464" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D464" s="7">
         <v>26</v>
@@ -12547,7 +12553,7 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -12563,13 +12569,13 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B466" s="6" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D466" s="7">
         <v>30</v>
@@ -12583,7 +12589,7 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -12599,13 +12605,13 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D468" s="7">
         <v>19</v>
@@ -12619,13 +12625,13 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B469" s="6" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D469" s="7">
         <v>23</v>
@@ -12639,13 +12645,13 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B470" s="6" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D470" s="7">
         <v>43</v>
@@ -12659,13 +12665,13 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B471" s="6" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D471" s="7">
         <v>44</v>
@@ -12679,13 +12685,13 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B472" s="6" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D472" s="7">
         <v>51</v>
@@ -12699,13 +12705,13 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B473" s="6" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D473" s="7">
         <v>33</v>
@@ -12719,13 +12725,13 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D474" s="7">
         <v>20</v>
@@ -12739,13 +12745,13 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B475" s="6" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D475" s="7">
         <v>50</v>
@@ -12759,13 +12765,13 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B476" s="6" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D476" s="7">
         <v>414</v>
@@ -12779,13 +12785,13 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B477" s="6" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D477" s="7">
         <v>30</v>
@@ -12799,13 +12805,13 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B478" s="6" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D478" s="7">
         <v>401</v>
@@ -12819,13 +12825,13 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B479" s="6" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D479" s="7">
         <v>243</v>
@@ -12839,13 +12845,13 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B480" s="6" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D480" s="7">
         <v>20</v>
@@ -12859,13 +12865,13 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B481" s="6" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D481" s="7">
         <v>20</v>
@@ -12879,13 +12885,13 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B482" s="6" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D482" s="7">
         <v>203</v>
@@ -12899,13 +12905,13 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B483" s="6" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D483" s="7">
         <v>17</v>
@@ -12919,13 +12925,13 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B484" s="6" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D484" s="7">
         <v>100</v>
@@ -12939,13 +12945,13 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B485" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D485" s="7">
         <v>33</v>
@@ -12959,13 +12965,13 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B486" s="6" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D486" s="7">
         <v>47</v>
@@ -12979,13 +12985,13 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B487" s="6" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D487" s="7">
         <v>20</v>
@@ -12999,13 +13005,13 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B488" s="6" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D488" s="7">
         <v>100</v>
@@ -13019,13 +13025,13 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489" s="6" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B489" s="6" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D489" s="7">
         <v>51</v>
@@ -13039,13 +13045,13 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490" s="6" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B490" s="6" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D490" s="7">
         <v>13</v>
@@ -13059,13 +13065,13 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491" s="6" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B491" s="6" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D491" s="7">
         <v>14</v>
@@ -13079,13 +13085,13 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492" s="6" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B492" s="6" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D492" s="7">
         <v>58</v>
@@ -13099,13 +13105,13 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493" s="6" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B493" s="6" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D493" s="7">
         <v>14</v>
@@ -13119,13 +13125,13 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494" s="6" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B494" s="6" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D494" s="7">
         <v>22</v>
@@ -13139,13 +13145,13 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495" s="6" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B495" s="6" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D495" s="7">
         <v>16</v>
@@ -13159,13 +13165,13 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496" s="6" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B496" s="6" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D496" s="7">
         <v>15</v>
@@ -13179,13 +13185,13 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" s="6" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B497" s="6" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D497" s="7">
         <v>29</v>
@@ -13199,13 +13205,13 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" s="6" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B498" s="6" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D498" s="7">
         <v>77</v>
@@ -13219,13 +13225,13 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" s="6" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B499" s="6" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D499" s="7">
         <v>19</v>
@@ -13239,13 +13245,13 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500" s="6" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B500" s="6" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D500" s="7">
         <v>30</v>
@@ -13259,13 +13265,13 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501" s="6" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B501" s="6" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D501" s="7">
         <v>24</v>
@@ -13279,13 +13285,13 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="6" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B502" s="6" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D502" s="7">
         <v>13</v>
@@ -13299,7 +13305,7 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -13315,10 +13321,10 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" s="6" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B504" s="6" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C504" s="6"/>
       <c r="D504" s="7">
@@ -13333,10 +13339,10 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" s="6" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B505" s="6" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C505" s="6"/>
       <c r="D505" s="7">

--- a/temp_LISTA_S_corregida.xlsx
+++ b/temp_LISTA_S_corregida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edgar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4F843F-120D-4572-8C46-17C898EBF9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5892DF6-5305-4B8D-91BA-D16DA20C674C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$6:$D$505</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$6:$D$503</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="1000">
   <si>
     <t>LISTA   S    AL   14/09/2026</t>
   </si>
@@ -1297,12 +1297,6 @@
     <t>HIKVISION ROUTER WIFI DS-3WR12GC AC1200</t>
   </si>
   <si>
-    <t>DS-D5019S0-1P0</t>
-  </si>
-  <si>
-    <t>HIKVISION MONITOR LED 18.5 75Hz HD HDMI VGA</t>
-  </si>
-  <si>
     <t>DS-D5024FN10</t>
   </si>
   <si>
@@ -1997,12 +1991,6 @@
   </si>
   <si>
     <t>LOGITECH TECLADO PEBBLE KEYS 2 K380S INALAMBRICO BLUETOOTH ESPAÑOL</t>
-  </si>
-  <si>
-    <t>920-013445</t>
-  </si>
-  <si>
-    <t>LOGITECH K250 - TECLADO INALAMBRICO BLUETOOTH, ESP, NEGRO</t>
   </si>
   <si>
     <t>920-013513</t>
@@ -3499,7 +3487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F505"/>
+  <dimension ref="A2:F503"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
@@ -3829,7 +3817,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>37</v>
@@ -3849,7 +3837,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>38</v>
@@ -3869,7 +3857,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>39</v>
@@ -7674,13 +7662,13 @@
         <v>411</v>
       </c>
       <c r="D217" s="7">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E217" s="10">
-        <v>0</v>
+        <v>143.25</v>
       </c>
       <c r="F217" s="11">
-        <v>0</v>
+        <v>199.88372093023261</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7694,69 +7682,69 @@
         <v>411</v>
       </c>
       <c r="D218" s="7">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E218" s="10">
-        <v>143.25</v>
+        <v>123.25</v>
       </c>
       <c r="F218" s="11">
-        <v>199.88372093023261</v>
+        <v>171.97674418604649</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="6" t="s">
+      <c r="A219" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B219" s="6" t="s">
+      <c r="B219" s="4"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="5">
+        <v>5745</v>
+      </c>
+      <c r="E219" s="10">
+        <v>17828.566666666669</v>
+      </c>
+      <c r="F219" s="11">
+        <v>24877.069767441859</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D219" s="7">
-        <v>65</v>
-      </c>
-      <c r="E219" s="10">
-        <v>123.25</v>
-      </c>
-      <c r="F219" s="11">
-        <v>171.97674418604649</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A220" s="4" t="s">
+      <c r="B220" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="5">
-        <v>5745</v>
+      <c r="C220" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D220" s="7">
+        <v>21</v>
       </c>
       <c r="E220" s="10">
-        <v>17828.566666666669</v>
+        <v>1666.583333333333</v>
       </c>
       <c r="F220" s="11">
-        <v>24877.069767441859</v>
+        <v>2325.4651162790701</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C221" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="B221" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>433</v>
-      </c>
       <c r="D221" s="7">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="E221" s="10">
-        <v>1666.583333333333</v>
+        <v>307.08333333333343</v>
       </c>
       <c r="F221" s="11">
-        <v>2325.4651162790701</v>
+        <v>428.48837209302332</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -7767,16 +7755,16 @@
         <v>435</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D222" s="7">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="E222" s="10">
-        <v>307.08333333333343</v>
+        <v>16.333333333333339</v>
       </c>
       <c r="F222" s="11">
-        <v>428.48837209302332</v>
+        <v>22.79069767441861</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -7787,16 +7775,16 @@
         <v>437</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D223" s="7">
-        <v>158</v>
+        <v>828</v>
       </c>
       <c r="E223" s="10">
-        <v>16.333333333333339</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F223" s="11">
-        <v>22.79069767441861</v>
+        <v>6.8604651162790704</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -7807,16 +7795,16 @@
         <v>439</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D224" s="7">
-        <v>828</v>
+        <v>191</v>
       </c>
       <c r="E224" s="10">
-        <v>4.916666666666667</v>
+        <v>22.25</v>
       </c>
       <c r="F224" s="11">
-        <v>6.8604651162790704</v>
+        <v>31.04651162790698</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -7827,10 +7815,10 @@
         <v>441</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D225" s="7">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="E225" s="10">
         <v>22.25</v>
@@ -7847,16 +7835,16 @@
         <v>443</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D226" s="7">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E226" s="10">
-        <v>22.25</v>
+        <v>274.08333333333331</v>
       </c>
       <c r="F226" s="11">
-        <v>31.04651162790698</v>
+        <v>382.44186046511618</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -7867,16 +7855,16 @@
         <v>445</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D227" s="7">
         <v>125</v>
       </c>
       <c r="E227" s="10">
-        <v>274.08333333333331</v>
+        <v>408.16666666666669</v>
       </c>
       <c r="F227" s="11">
-        <v>382.44186046511618</v>
+        <v>569.53488372093022</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -7887,16 +7875,16 @@
         <v>447</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D228" s="7">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="E228" s="10">
-        <v>408.16666666666669</v>
+        <v>183.33333333333329</v>
       </c>
       <c r="F228" s="11">
-        <v>569.53488372093022</v>
+        <v>255.81395348837211</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -7907,16 +7895,16 @@
         <v>449</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D229" s="7">
-        <v>37</v>
+        <v>342</v>
       </c>
       <c r="E229" s="10">
-        <v>183.33333333333329</v>
+        <v>443.33333333333343</v>
       </c>
       <c r="F229" s="11">
-        <v>255.81395348837211</v>
+        <v>618.60465116279067</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -7927,16 +7915,16 @@
         <v>451</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D230" s="7">
-        <v>342</v>
+        <v>11</v>
       </c>
       <c r="E230" s="10">
-        <v>443.33333333333343</v>
+        <v>2191.666666666667</v>
       </c>
       <c r="F230" s="11">
-        <v>618.60465116279067</v>
+        <v>3058.1395348837209</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -7947,16 +7935,16 @@
         <v>453</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D231" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E231" s="10">
-        <v>2191.666666666667</v>
+        <v>1547.083333333333</v>
       </c>
       <c r="F231" s="11">
-        <v>3058.1395348837209</v>
+        <v>2158.7209302325582</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
@@ -7967,16 +7955,16 @@
         <v>455</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D232" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E232" s="10">
-        <v>1547.083333333333</v>
+        <v>21.5</v>
       </c>
       <c r="F232" s="11">
-        <v>2158.7209302325582</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -7987,10 +7975,10 @@
         <v>457</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D233" s="7">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E233" s="10">
         <v>21.5</v>
@@ -8007,16 +7995,16 @@
         <v>459</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D234" s="7">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E234" s="10">
-        <v>21.5</v>
+        <v>16.333333333333339</v>
       </c>
       <c r="F234" s="11">
-        <v>30</v>
+        <v>22.79069767441861</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -8027,16 +8015,16 @@
         <v>461</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D235" s="7">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="E235" s="10">
-        <v>16.333333333333339</v>
+        <v>1.666666666666667E-2</v>
       </c>
       <c r="F235" s="11">
-        <v>22.79069767441861</v>
+        <v>2.3255813953488368E-2</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -8047,16 +8035,16 @@
         <v>463</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D236" s="7">
-        <v>172</v>
+        <v>589</v>
       </c>
       <c r="E236" s="10">
-        <v>1.666666666666667E-2</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F236" s="11">
-        <v>2.3255813953488368E-2</v>
+        <v>6.8604651162790704</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -8067,16 +8055,16 @@
         <v>465</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D237" s="7">
-        <v>589</v>
+        <v>96</v>
       </c>
       <c r="E237" s="10">
-        <v>4.916666666666667</v>
+        <v>16.333333333333339</v>
       </c>
       <c r="F237" s="11">
-        <v>6.8604651162790704</v>
+        <v>22.79069767441861</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -8087,16 +8075,16 @@
         <v>467</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D238" s="7">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E238" s="10">
-        <v>16.333333333333339</v>
+        <v>1.666666666666667E-2</v>
       </c>
       <c r="F238" s="11">
-        <v>22.79069767441861</v>
+        <v>2.3255813953488368E-2</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -8107,16 +8095,16 @@
         <v>469</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D239" s="7">
-        <v>172</v>
+        <v>721</v>
       </c>
       <c r="E239" s="10">
-        <v>1.666666666666667E-2</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F239" s="11">
-        <v>2.3255813953488368E-2</v>
+        <v>6.8604651162790704</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -8127,16 +8115,16 @@
         <v>471</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D240" s="7">
-        <v>721</v>
+        <v>96</v>
       </c>
       <c r="E240" s="10">
-        <v>4.916666666666667</v>
+        <v>16.333333333333339</v>
       </c>
       <c r="F240" s="11">
-        <v>6.8604651162790704</v>
+        <v>22.79069767441861</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -8147,16 +8135,16 @@
         <v>473</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D241" s="7">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E241" s="10">
-        <v>16.333333333333339</v>
+        <v>1.666666666666667E-2</v>
       </c>
       <c r="F241" s="11">
-        <v>22.79069767441861</v>
+        <v>2.3255813953488368E-2</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -8167,16 +8155,16 @@
         <v>475</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D242" s="7">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="E242" s="10">
-        <v>1.666666666666667E-2</v>
+        <v>43.333333333333343</v>
       </c>
       <c r="F242" s="11">
-        <v>2.3255813953488368E-2</v>
+        <v>60.465116279069768</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -8187,16 +8175,16 @@
         <v>477</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D243" s="7">
-        <v>134</v>
+        <v>667</v>
       </c>
       <c r="E243" s="10">
-        <v>43.333333333333343</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F243" s="11">
-        <v>60.465116279069768</v>
+        <v>6.8604651162790704</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -8207,16 +8195,16 @@
         <v>479</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D244" s="7">
-        <v>667</v>
+        <v>202</v>
       </c>
       <c r="E244" s="10">
-        <v>4.916666666666667</v>
+        <v>110</v>
       </c>
       <c r="F244" s="11">
-        <v>6.8604651162790704</v>
+        <v>153.48837209302329</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -8227,10 +8215,10 @@
         <v>481</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D245" s="7">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="E245" s="10">
         <v>110</v>
@@ -8247,72 +8235,72 @@
         <v>483</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D246" s="7">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="E246" s="10">
-        <v>110</v>
+        <v>251.16666666666671</v>
       </c>
       <c r="F246" s="11">
-        <v>153.48837209302329</v>
+        <v>350.46511627906972</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B247" s="6" t="s">
+      <c r="B247" s="4"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="5">
+        <v>3800</v>
+      </c>
+      <c r="E247" s="10">
+        <v>1756.083333333333</v>
+      </c>
+      <c r="F247" s="11">
+        <v>2450.348837209302</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C247" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="D247" s="7">
-        <v>92</v>
-      </c>
-      <c r="E247" s="10">
-        <v>251.16666666666671</v>
-      </c>
-      <c r="F247" s="11">
-        <v>350.46511627906972</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A248" s="4" t="s">
+      <c r="B248" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="B248" s="4"/>
-      <c r="C248" s="4"/>
-      <c r="D248" s="5">
-        <v>3800</v>
+      <c r="C248" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D248" s="7">
+        <v>596</v>
       </c>
       <c r="E248" s="10">
-        <v>1756.083333333333</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="F248" s="11">
-        <v>2450.348837209302</v>
+        <v>15.46511627906977</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C249" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="B249" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>489</v>
-      </c>
       <c r="D249" s="7">
-        <v>596</v>
+        <v>517</v>
       </c>
       <c r="E249" s="10">
-        <v>11.08333333333333</v>
+        <v>18.333333333333339</v>
       </c>
       <c r="F249" s="11">
-        <v>15.46511627906977</v>
+        <v>25.581395348837209</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -8323,16 +8311,16 @@
         <v>491</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D250" s="7">
-        <v>517</v>
+        <v>296</v>
       </c>
       <c r="E250" s="10">
-        <v>18.333333333333339</v>
+        <v>42.166666666666671</v>
       </c>
       <c r="F250" s="11">
-        <v>25.581395348837209</v>
+        <v>58.837209302325583</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -8343,16 +8331,16 @@
         <v>493</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D251" s="7">
-        <v>296</v>
+        <v>897</v>
       </c>
       <c r="E251" s="10">
-        <v>42.166666666666671</v>
+        <v>18.333333333333339</v>
       </c>
       <c r="F251" s="11">
-        <v>58.837209302325583</v>
+        <v>25.581395348837209</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -8363,16 +8351,16 @@
         <v>495</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D252" s="7">
-        <v>897</v>
+        <v>264</v>
       </c>
       <c r="E252" s="10">
-        <v>18.333333333333339</v>
+        <v>42.166666666666671</v>
       </c>
       <c r="F252" s="11">
-        <v>25.581395348837209</v>
+        <v>58.837209302325583</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -8383,16 +8371,16 @@
         <v>497</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D253" s="7">
-        <v>264</v>
+        <v>613</v>
       </c>
       <c r="E253" s="10">
-        <v>42.166666666666671</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="F253" s="11">
-        <v>58.837209302325583</v>
+        <v>15.46511627906977</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -8403,16 +8391,16 @@
         <v>499</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D254" s="7">
-        <v>613</v>
+        <v>100</v>
       </c>
       <c r="E254" s="10">
-        <v>11.08333333333333</v>
+        <v>326.16666666666669</v>
       </c>
       <c r="F254" s="11">
-        <v>15.46511627906977</v>
+        <v>455.11627906976742</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
@@ -8423,16 +8411,16 @@
         <v>501</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D255" s="7">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="E255" s="10">
-        <v>326.16666666666669</v>
+        <v>303.66666666666669</v>
       </c>
       <c r="F255" s="11">
-        <v>455.11627906976742</v>
+        <v>423.72093023255809</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -8443,16 +8431,16 @@
         <v>503</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D256" s="7">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E256" s="10">
-        <v>303.66666666666669</v>
+        <v>120.4</v>
       </c>
       <c r="F256" s="11">
-        <v>423.72093023255809</v>
+        <v>168</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -8463,16 +8451,16 @@
         <v>505</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D257" s="7">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E257" s="10">
-        <v>120.4</v>
+        <v>186.06666666666669</v>
       </c>
       <c r="F257" s="11">
-        <v>168</v>
+        <v>259.62790697674421</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -8483,16 +8471,16 @@
         <v>507</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D258" s="7">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="E258" s="10">
-        <v>186.06666666666669</v>
+        <v>314.91666666666669</v>
       </c>
       <c r="F258" s="11">
-        <v>259.62790697674421</v>
+        <v>439.41860465116281</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -8503,72 +8491,72 @@
         <v>509</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D259" s="7">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="E259" s="10">
-        <v>314.91666666666669</v>
+        <v>326.16666666666669</v>
       </c>
       <c r="F259" s="11">
-        <v>439.41860465116281</v>
+        <v>455.11627906976742</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="6" t="s">
+      <c r="A260" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="B260" s="6" t="s">
+      <c r="B260" s="4"/>
+      <c r="C260" s="4"/>
+      <c r="D260" s="5">
+        <v>501</v>
+      </c>
+      <c r="E260" s="10">
+        <v>2410.166666666667</v>
+      </c>
+      <c r="F260" s="11">
+        <v>3363.0232558139528</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="C260" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="D260" s="7">
-        <v>195</v>
-      </c>
-      <c r="E260" s="10">
-        <v>326.16666666666669</v>
-      </c>
-      <c r="F260" s="11">
-        <v>455.11627906976742</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="4" t="s">
+      <c r="B261" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="B261" s="4"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="5">
-        <v>501</v>
+      <c r="C261" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="D261" s="7">
+        <v>19</v>
       </c>
       <c r="E261" s="10">
-        <v>2410.166666666667</v>
+        <v>27.166666666666671</v>
       </c>
       <c r="F261" s="11">
-        <v>3363.0232558139528</v>
+        <v>37.906976744186053</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C262" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="B262" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="C262" s="6" t="s">
-        <v>515</v>
-      </c>
       <c r="D262" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E262" s="10">
-        <v>27.166666666666671</v>
+        <v>26.25</v>
       </c>
       <c r="F262" s="11">
-        <v>37.906976744186053</v>
+        <v>36.627906976744192</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -8579,16 +8567,16 @@
         <v>517</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D263" s="7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E263" s="10">
-        <v>26.25</v>
+        <v>27.166666666666671</v>
       </c>
       <c r="F263" s="11">
-        <v>36.627906976744192</v>
+        <v>37.906976744186053</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -8599,16 +8587,16 @@
         <v>519</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D264" s="7">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E264" s="10">
-        <v>27.166666666666671</v>
+        <v>32.083333333333343</v>
       </c>
       <c r="F264" s="11">
-        <v>37.906976744186053</v>
+        <v>44.767441860465119</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -8619,16 +8607,16 @@
         <v>521</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D265" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E265" s="10">
-        <v>32.083333333333343</v>
+        <v>34.583333333333343</v>
       </c>
       <c r="F265" s="11">
-        <v>44.767441860465119</v>
+        <v>48.255813953488371</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -8639,16 +8627,16 @@
         <v>523</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D266" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E266" s="10">
-        <v>34.583333333333343</v>
+        <v>73.166666666666671</v>
       </c>
       <c r="F266" s="11">
-        <v>48.255813953488371</v>
+        <v>102.0930232558139</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
@@ -8659,16 +8647,16 @@
         <v>525</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D267" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E267" s="10">
-        <v>73.166666666666671</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="F267" s="11">
-        <v>102.0930232558139</v>
+        <v>15.46511627906977</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -8679,16 +8667,16 @@
         <v>527</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D268" s="7">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E268" s="10">
-        <v>11.08333333333333</v>
+        <v>26.083333333333339</v>
       </c>
       <c r="F268" s="11">
-        <v>15.46511627906977</v>
+        <v>36.395348837209298</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -8699,16 +8687,16 @@
         <v>529</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D269" s="7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E269" s="10">
-        <v>26.083333333333339</v>
+        <v>24.666666666666671</v>
       </c>
       <c r="F269" s="11">
-        <v>36.395348837209298</v>
+        <v>34.418604651162788</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -8719,16 +8707,16 @@
         <v>531</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D270" s="7">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E270" s="10">
-        <v>24.666666666666671</v>
+        <v>37.083333333333343</v>
       </c>
       <c r="F270" s="11">
-        <v>34.418604651162788</v>
+        <v>51.744186046511629</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
@@ -8739,16 +8727,16 @@
         <v>533</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D271" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E271" s="10">
-        <v>37.083333333333343</v>
+        <v>22.083333333333339</v>
       </c>
       <c r="F271" s="11">
-        <v>51.744186046511629</v>
+        <v>30.813953488372089</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -8759,19 +8747,19 @@
         <v>535</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D272" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E272" s="10">
-        <v>22.083333333333339</v>
+        <v>21.25</v>
       </c>
       <c r="F272" s="11">
-        <v>30.813953488372089</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29.651162790697679</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>536</v>
       </c>
@@ -8779,19 +8767,19 @@
         <v>537</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D273" s="7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E273" s="10">
-        <v>21.25</v>
+        <v>20.833333333333339</v>
       </c>
       <c r="F273" s="11">
-        <v>29.651162790697679</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29.069767441860471</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
         <v>538</v>
       </c>
@@ -8799,16 +8787,16 @@
         <v>539</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D274" s="7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E274" s="10">
-        <v>20.833333333333339</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="F274" s="11">
-        <v>29.069767441860471</v>
+        <v>5.3488372093023253</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -8819,72 +8807,72 @@
         <v>541</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D275" s="7">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E275" s="10">
-        <v>3.833333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="F275" s="11">
-        <v>5.3488372093023253</v>
+        <v>12.209302325581399</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A276" s="6" t="s">
+      <c r="A276" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B276" s="6" t="s">
+      <c r="B276" s="4"/>
+      <c r="C276" s="4"/>
+      <c r="D276" s="5">
+        <v>186</v>
+      </c>
+      <c r="E276" s="10">
+        <v>301.75000000000011</v>
+      </c>
+      <c r="F276" s="11">
+        <v>421.04651162790702</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="C276" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D276" s="7">
-        <v>31</v>
-      </c>
-      <c r="E276" s="10">
-        <v>8.75</v>
-      </c>
-      <c r="F276" s="11">
-        <v>12.209302325581399</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A277" s="4" t="s">
+      <c r="B277" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="B277" s="4"/>
-      <c r="C277" s="4"/>
-      <c r="D277" s="5">
-        <v>186</v>
+      <c r="C277" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D277" s="7">
+        <v>56</v>
       </c>
       <c r="E277" s="10">
-        <v>301.75000000000011</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="F277" s="11">
-        <v>421.04651162790702</v>
+        <v>19.767441860465119</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="C278" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="B278" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="C278" s="6" t="s">
-        <v>547</v>
-      </c>
       <c r="D278" s="7">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E278" s="10">
-        <v>14.16666666666667</v>
+        <v>18.166666666666671</v>
       </c>
       <c r="F278" s="11">
-        <v>19.767441860465119</v>
+        <v>25.348837209302332</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
@@ -8895,72 +8883,72 @@
         <v>549</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D279" s="7">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E279" s="10">
-        <v>18.166666666666671</v>
+        <v>24.583333333333339</v>
       </c>
       <c r="F279" s="11">
-        <v>25.348837209302332</v>
+        <v>34.302325581395351</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="B280" s="6" t="s">
+      <c r="B280" s="4"/>
+      <c r="C280" s="4"/>
+      <c r="D280" s="5">
+        <v>117</v>
+      </c>
+      <c r="E280" s="10">
+        <v>480.50000000000011</v>
+      </c>
+      <c r="F280" s="11">
+        <v>670.46511627906978</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="C280" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="D280" s="7">
-        <v>19</v>
-      </c>
-      <c r="E280" s="10">
-        <v>24.583333333333339</v>
-      </c>
-      <c r="F280" s="11">
-        <v>34.302325581395351</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A281" s="4" t="s">
+      <c r="B281" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="5">
-        <v>117</v>
+      <c r="C281" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D281" s="7">
+        <v>26</v>
       </c>
       <c r="E281" s="10">
-        <v>480.50000000000011</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="F281" s="11">
-        <v>670.46511627906978</v>
+        <v>93.023255813953483</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C282" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="B282" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="C282" s="6" t="s">
-        <v>555</v>
-      </c>
       <c r="D282" s="7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E282" s="10">
-        <v>66.666666666666671</v>
+        <v>173.83333333333329</v>
       </c>
       <c r="F282" s="11">
-        <v>93.023255813953483</v>
+        <v>242.55813953488371</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -8971,66 +8959,66 @@
         <v>557</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D283" s="7">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="E283" s="10">
-        <v>173.83333333333329</v>
+        <v>165</v>
       </c>
       <c r="F283" s="11">
-        <v>242.55813953488371</v>
+        <v>230.23255813953489</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A284" s="6" t="s">
+      <c r="A284" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="B284" s="6" t="s">
+      <c r="B284" s="4"/>
+      <c r="C284" s="4"/>
+      <c r="D284" s="5">
+        <v>4776</v>
+      </c>
+      <c r="E284" s="10">
+        <v>6090.5833333333321</v>
+      </c>
+      <c r="F284" s="11">
+        <v>8498.4883720930211</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="C284" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="D284" s="7">
-        <v>58</v>
-      </c>
-      <c r="E284" s="10">
-        <v>165</v>
-      </c>
-      <c r="F284" s="11">
-        <v>230.23255813953489</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A285" s="4" t="s">
+      <c r="B285" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="B285" s="4"/>
-      <c r="C285" s="4"/>
-      <c r="D285" s="5">
-        <v>4776</v>
+      <c r="C285" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D285" s="7">
+        <v>19</v>
       </c>
       <c r="E285" s="10">
-        <v>6090.5833333333321</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="F285" s="11">
-        <v>8498.4883720930211</v>
+        <v>120.93023255813949</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="C286" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="B286" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="C286" s="6" t="s">
-        <v>563</v>
-      </c>
       <c r="D286" s="7">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="E286" s="10">
         <v>86.666666666666671</v>
@@ -9047,16 +9035,16 @@
         <v>565</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D287" s="7">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E287" s="10">
-        <v>86.666666666666671</v>
+        <v>22.083333333333339</v>
       </c>
       <c r="F287" s="11">
-        <v>120.93023255813949</v>
+        <v>30.813953488372089</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -9067,16 +9055,16 @@
         <v>567</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D288" s="7">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E288" s="10">
-        <v>22.083333333333339</v>
+        <v>37.083333333333343</v>
       </c>
       <c r="F288" s="11">
-        <v>30.813953488372089</v>
+        <v>51.744186046511629</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -9087,16 +9075,16 @@
         <v>569</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D289" s="7">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="E289" s="10">
-        <v>37.083333333333343</v>
+        <v>31.583333333333329</v>
       </c>
       <c r="F289" s="11">
-        <v>51.744186046511629</v>
+        <v>44.069767441860463</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -9107,16 +9095,16 @@
         <v>571</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D290" s="7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E290" s="10">
-        <v>31.583333333333329</v>
+        <v>29.25</v>
       </c>
       <c r="F290" s="11">
-        <v>44.069767441860463</v>
+        <v>40.813953488372093</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
@@ -9127,16 +9115,16 @@
         <v>573</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D291" s="7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E291" s="10">
-        <v>29.25</v>
+        <v>32.5</v>
       </c>
       <c r="F291" s="11">
-        <v>40.813953488372093</v>
+        <v>45.348837209302317</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -9147,16 +9135,16 @@
         <v>575</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D292" s="7">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="E292" s="10">
-        <v>32.5</v>
+        <v>17.333333333333339</v>
       </c>
       <c r="F292" s="11">
-        <v>45.348837209302317</v>
+        <v>24.186046511627911</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -9167,16 +9155,16 @@
         <v>577</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D293" s="7">
-        <v>261</v>
+        <v>24</v>
       </c>
       <c r="E293" s="10">
-        <v>17.333333333333339</v>
+        <v>63.250000000000007</v>
       </c>
       <c r="F293" s="11">
-        <v>24.186046511627911</v>
+        <v>88.255813953488385</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -9187,16 +9175,16 @@
         <v>579</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D294" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E294" s="10">
-        <v>63.250000000000007</v>
+        <v>79.666666666666671</v>
       </c>
       <c r="F294" s="11">
-        <v>88.255813953488385</v>
+        <v>111.1627906976744</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -9207,16 +9195,16 @@
         <v>581</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D295" s="7">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="E295" s="10">
-        <v>79.666666666666671</v>
+        <v>29.166666666666671</v>
       </c>
       <c r="F295" s="11">
-        <v>111.1627906976744</v>
+        <v>40.697674418604649</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -9227,16 +9215,16 @@
         <v>583</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D296" s="7">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="E296" s="10">
-        <v>29.166666666666671</v>
+        <v>30.833333333333339</v>
       </c>
       <c r="F296" s="11">
-        <v>40.697674418604649</v>
+        <v>43.02325581395349</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
@@ -9247,16 +9235,16 @@
         <v>585</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D297" s="7">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="E297" s="10">
-        <v>30.833333333333339</v>
+        <v>37.666666666666671</v>
       </c>
       <c r="F297" s="11">
-        <v>43.02325581395349</v>
+        <v>52.558139534883722</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -9267,10 +9255,10 @@
         <v>587</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D298" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E298" s="10">
         <v>37.666666666666671</v>
@@ -9287,16 +9275,16 @@
         <v>589</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D299" s="7">
-        <v>292</v>
+        <v>15</v>
       </c>
       <c r="E299" s="10">
-        <v>37.666666666666671</v>
+        <v>70.25</v>
       </c>
       <c r="F299" s="11">
-        <v>52.558139534883722</v>
+        <v>98.023255813953483</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -9307,16 +9295,16 @@
         <v>591</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D300" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E300" s="10">
-        <v>70.25</v>
+        <v>62.833333333333343</v>
       </c>
       <c r="F300" s="11">
-        <v>98.023255813953483</v>
+        <v>87.674418604651166</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -9327,16 +9315,16 @@
         <v>593</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D301" s="7">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="E301" s="10">
-        <v>62.833333333333343</v>
+        <v>192</v>
       </c>
       <c r="F301" s="11">
-        <v>87.674418604651166</v>
+        <v>267.90697674418612</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -9347,16 +9335,16 @@
         <v>595</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D302" s="7">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="E302" s="10">
-        <v>192</v>
+        <v>50.833333333333343</v>
       </c>
       <c r="F302" s="11">
-        <v>267.90697674418612</v>
+        <v>70.930232558139537</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
@@ -9367,16 +9355,16 @@
         <v>597</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D303" s="7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E303" s="10">
-        <v>50.833333333333343</v>
+        <v>68.333333333333343</v>
       </c>
       <c r="F303" s="11">
-        <v>70.930232558139537</v>
+        <v>95.348837209302332</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -9387,16 +9375,16 @@
         <v>599</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D304" s="7">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E304" s="10">
-        <v>68.333333333333343</v>
+        <v>196.66666666666671</v>
       </c>
       <c r="F304" s="11">
-        <v>95.348837209302332</v>
+        <v>274.41860465116281</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -9407,16 +9395,16 @@
         <v>601</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D305" s="7">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="E305" s="10">
-        <v>196.66666666666671</v>
+        <v>107.0833333333333</v>
       </c>
       <c r="F305" s="11">
-        <v>274.41860465116281</v>
+        <v>149.41860465116281</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
@@ -9427,16 +9415,16 @@
         <v>603</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D306" s="7">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E306" s="10">
-        <v>107.0833333333333</v>
+        <v>115</v>
       </c>
       <c r="F306" s="11">
-        <v>149.41860465116281</v>
+        <v>160.4651162790698</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -9447,16 +9435,16 @@
         <v>605</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D307" s="7">
-        <v>43</v>
+        <v>333</v>
       </c>
       <c r="E307" s="10">
-        <v>115</v>
+        <v>17.333333333333339</v>
       </c>
       <c r="F307" s="11">
-        <v>160.4651162790698</v>
+        <v>24.186046511627911</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
@@ -9467,16 +9455,16 @@
         <v>607</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D308" s="7">
-        <v>333</v>
+        <v>126</v>
       </c>
       <c r="E308" s="10">
-        <v>17.333333333333339</v>
+        <v>18.25</v>
       </c>
       <c r="F308" s="11">
-        <v>24.186046511627911</v>
+        <v>25.465116279069761</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -9487,16 +9475,16 @@
         <v>609</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D309" s="7">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="E309" s="10">
-        <v>18.25</v>
+        <v>26.583333333333329</v>
       </c>
       <c r="F309" s="11">
-        <v>25.465116279069761</v>
+        <v>37.093023255813947</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
@@ -9507,16 +9495,16 @@
         <v>611</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D310" s="7">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E310" s="10">
-        <v>26.583333333333329</v>
+        <v>29</v>
       </c>
       <c r="F310" s="11">
-        <v>37.093023255813947</v>
+        <v>40.465116279069768</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -9527,16 +9515,16 @@
         <v>613</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D311" s="7">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="E311" s="10">
-        <v>29</v>
+        <v>26.583333333333329</v>
       </c>
       <c r="F311" s="11">
-        <v>40.465116279069768</v>
+        <v>37.093023255813947</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -9547,10 +9535,10 @@
         <v>615</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D312" s="7">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="E312" s="10">
         <v>26.583333333333329</v>
@@ -9567,16 +9555,16 @@
         <v>617</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D313" s="7">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="E313" s="10">
-        <v>26.583333333333329</v>
+        <v>17.083333333333339</v>
       </c>
       <c r="F313" s="11">
-        <v>37.093023255813947</v>
+        <v>23.837209302325579</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -9587,16 +9575,16 @@
         <v>619</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D314" s="7">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="E314" s="10">
-        <v>17.083333333333339</v>
+        <v>16.583333333333339</v>
       </c>
       <c r="F314" s="11">
-        <v>23.837209302325579</v>
+        <v>23.13953488372093</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
@@ -9607,10 +9595,10 @@
         <v>621</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D315" s="7">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E315" s="10">
         <v>16.583333333333339</v>
@@ -9627,16 +9615,16 @@
         <v>623</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D316" s="7">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E316" s="10">
-        <v>16.583333333333339</v>
+        <v>18.333333333333339</v>
       </c>
       <c r="F316" s="11">
-        <v>23.13953488372093</v>
+        <v>25.581395348837209</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -9647,16 +9635,16 @@
         <v>625</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D317" s="7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E317" s="10">
-        <v>18.333333333333339</v>
+        <v>39.916666666666657</v>
       </c>
       <c r="F317" s="11">
-        <v>25.581395348837209</v>
+        <v>55.697674418604649</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -9667,16 +9655,16 @@
         <v>627</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D318" s="7">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="E318" s="10">
-        <v>39.916666666666657</v>
+        <v>32.666666666666671</v>
       </c>
       <c r="F318" s="11">
-        <v>55.697674418604649</v>
+        <v>45.581395348837212</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -9687,16 +9675,16 @@
         <v>629</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D319" s="7">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E319" s="10">
-        <v>32.666666666666671</v>
+        <v>44.916666666666657</v>
       </c>
       <c r="F319" s="11">
-        <v>45.581395348837212</v>
+        <v>62.674418604651159</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -9707,16 +9695,16 @@
         <v>631</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D320" s="7">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E320" s="10">
-        <v>44.916666666666657</v>
+        <v>67.833333333333343</v>
       </c>
       <c r="F320" s="11">
-        <v>62.674418604651159</v>
+        <v>94.651162790697683</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -9727,16 +9715,16 @@
         <v>633</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D321" s="7">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="E321" s="10">
-        <v>67.833333333333343</v>
+        <v>106</v>
       </c>
       <c r="F321" s="11">
-        <v>94.651162790697683</v>
+        <v>147.90697674418601</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -9747,16 +9735,16 @@
         <v>635</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D322" s="7">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E322" s="10">
-        <v>106</v>
+        <v>78.75</v>
       </c>
       <c r="F322" s="11">
-        <v>147.90697674418601</v>
+        <v>109.8837209302326</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
@@ -9767,16 +9755,16 @@
         <v>637</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D323" s="7">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E323" s="10">
-        <v>78.75</v>
+        <v>56.083333333333343</v>
       </c>
       <c r="F323" s="11">
-        <v>109.8837209302326</v>
+        <v>78.255813953488371</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -9787,16 +9775,16 @@
         <v>639</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D324" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E324" s="10">
-        <v>56.083333333333343</v>
+        <v>16.25</v>
       </c>
       <c r="F324" s="11">
-        <v>78.255813953488371</v>
+        <v>22.674418604651159</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -9807,16 +9795,16 @@
         <v>641</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D325" s="7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E325" s="10">
-        <v>16.25</v>
+        <v>208.75</v>
       </c>
       <c r="F325" s="11">
-        <v>22.674418604651159</v>
+        <v>291.27906976744191</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -9827,16 +9815,16 @@
         <v>643</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D326" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E326" s="10">
-        <v>208.75</v>
+        <v>72.833333333333343</v>
       </c>
       <c r="F326" s="11">
-        <v>291.27906976744191</v>
+        <v>101.6279069767442</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -9847,16 +9835,16 @@
         <v>645</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D327" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E327" s="10">
-        <v>72.833333333333343</v>
+        <v>76.333333333333329</v>
       </c>
       <c r="F327" s="11">
-        <v>101.6279069767442</v>
+        <v>106.5116279069767</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -9867,16 +9855,16 @@
         <v>647</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D328" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E328" s="10">
-        <v>76.333333333333329</v>
+        <v>65</v>
       </c>
       <c r="F328" s="11">
-        <v>106.5116279069767</v>
+        <v>90.697674418604649</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -9887,16 +9875,16 @@
         <v>649</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D329" s="7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E329" s="10">
-        <v>65</v>
+        <v>171.58333333333329</v>
       </c>
       <c r="F329" s="11">
-        <v>90.697674418604649</v>
+        <v>239.41860465116281</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -9907,16 +9895,16 @@
         <v>651</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D330" s="7">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E330" s="10">
-        <v>171.58333333333329</v>
+        <v>57.333333333333343</v>
       </c>
       <c r="F330" s="11">
-        <v>239.41860465116281</v>
+        <v>80</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -9927,10 +9915,10 @@
         <v>653</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D331" s="7">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E331" s="10">
         <v>57.333333333333343</v>
@@ -9947,10 +9935,10 @@
         <v>655</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D332" s="7">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E332" s="10">
         <v>57.333333333333343</v>
@@ -9967,16 +9955,16 @@
         <v>657</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D333" s="7">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="E333" s="10">
-        <v>57.333333333333343</v>
+        <v>42.666666666666671</v>
       </c>
       <c r="F333" s="11">
-        <v>80</v>
+        <v>59.534883720930239</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -9987,16 +9975,16 @@
         <v>659</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D334" s="7">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="E334" s="10">
-        <v>0</v>
+        <v>109.9166666666667</v>
       </c>
       <c r="F334" s="11">
-        <v>0</v>
+        <v>153.37209302325579</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -10007,16 +9995,16 @@
         <v>661</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D335" s="7">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="E335" s="10">
-        <v>42.666666666666671</v>
+        <v>108.75</v>
       </c>
       <c r="F335" s="11">
-        <v>59.534883720930239</v>
+        <v>151.7441860465116</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -10027,10 +10015,10 @@
         <v>663</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D336" s="7">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E336" s="10">
         <v>109.9166666666667</v>
@@ -10047,16 +10035,16 @@
         <v>665</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D337" s="7">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E337" s="10">
-        <v>108.75</v>
+        <v>109.9166666666667</v>
       </c>
       <c r="F337" s="11">
-        <v>151.7441860465116</v>
+        <v>153.37209302325579</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
@@ -10067,10 +10055,10 @@
         <v>667</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D338" s="7">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E338" s="10">
         <v>109.9166666666667</v>
@@ -10087,16 +10075,16 @@
         <v>669</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D339" s="7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E339" s="10">
-        <v>109.9166666666667</v>
+        <v>34.916666666666657</v>
       </c>
       <c r="F339" s="11">
-        <v>153.37209302325579</v>
+        <v>48.720930232558139</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -10107,16 +10095,16 @@
         <v>671</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D340" s="7">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E340" s="10">
-        <v>109.9166666666667</v>
+        <v>94.333333333333343</v>
       </c>
       <c r="F340" s="11">
-        <v>153.37209302325579</v>
+        <v>131.62790697674421</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -10127,16 +10115,16 @@
         <v>673</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D341" s="7">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E341" s="10">
-        <v>34.916666666666657</v>
+        <v>631.16666666666663</v>
       </c>
       <c r="F341" s="11">
-        <v>48.720930232558139</v>
+        <v>880.69767441860461</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
@@ -10147,16 +10135,16 @@
         <v>675</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D342" s="7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E342" s="10">
-        <v>94.333333333333343</v>
+        <v>626.00000000000011</v>
       </c>
       <c r="F342" s="11">
-        <v>131.62790697674421</v>
+        <v>873.48837209302337</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
@@ -10167,16 +10155,16 @@
         <v>677</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D343" s="7">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E343" s="10">
-        <v>631.16666666666663</v>
+        <v>65</v>
       </c>
       <c r="F343" s="11">
-        <v>880.69767441860461</v>
+        <v>90.697674418604649</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -10187,16 +10175,16 @@
         <v>679</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D344" s="7">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E344" s="10">
-        <v>626.00000000000011</v>
+        <v>65.833333333333343</v>
       </c>
       <c r="F344" s="11">
-        <v>873.48837209302337</v>
+        <v>91.860465116279073</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -10207,16 +10195,16 @@
         <v>681</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D345" s="7">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E345" s="10">
-        <v>65</v>
+        <v>26.166666666666671</v>
       </c>
       <c r="F345" s="11">
-        <v>90.697674418604649</v>
+        <v>36.511627906976742</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -10227,16 +10215,16 @@
         <v>683</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D346" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E346" s="10">
-        <v>65.833333333333343</v>
+        <v>44.916666666666657</v>
       </c>
       <c r="F346" s="11">
-        <v>91.860465116279073</v>
+        <v>62.674418604651159</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -10247,16 +10235,16 @@
         <v>685</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D347" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E347" s="10">
-        <v>26.166666666666671</v>
+        <v>75.833333333333343</v>
       </c>
       <c r="F347" s="11">
-        <v>36.511627906976742</v>
+        <v>105.81395348837211</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -10267,16 +10255,16 @@
         <v>687</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D348" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E348" s="10">
-        <v>44.916666666666657</v>
+        <v>275.25</v>
       </c>
       <c r="F348" s="11">
-        <v>62.674418604651159</v>
+        <v>384.06976744186051</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
@@ -10287,16 +10275,16 @@
         <v>689</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D349" s="7">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="E349" s="10">
-        <v>75.833333333333343</v>
+        <v>36.000000000000007</v>
       </c>
       <c r="F349" s="11">
-        <v>105.81395348837211</v>
+        <v>50.232558139534888</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -10307,16 +10295,16 @@
         <v>691</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D350" s="7">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="E350" s="10">
-        <v>275.25</v>
+        <v>30.833333333333339</v>
       </c>
       <c r="F350" s="11">
-        <v>384.06976744186051</v>
+        <v>43.02325581395349</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -10327,16 +10315,16 @@
         <v>693</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D351" s="7">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="E351" s="10">
-        <v>36.000000000000007</v>
+        <v>69.666666666666671</v>
       </c>
       <c r="F351" s="11">
-        <v>50.232558139534888</v>
+        <v>97.20930232558139</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -10347,16 +10335,16 @@
         <v>695</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D352" s="7">
-        <v>198</v>
+        <v>58</v>
       </c>
       <c r="E352" s="10">
-        <v>30.833333333333339</v>
+        <v>69.666666666666671</v>
       </c>
       <c r="F352" s="11">
-        <v>43.02325581395349</v>
+        <v>97.20930232558139</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -10367,16 +10355,16 @@
         <v>697</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D353" s="7">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E353" s="10">
-        <v>69.666666666666671</v>
+        <v>193.66666666666671</v>
       </c>
       <c r="F353" s="11">
-        <v>97.20930232558139</v>
+        <v>270.23255813953489</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -10387,56 +10375,52 @@
         <v>699</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D354" s="7">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E354" s="10">
-        <v>69.666666666666671</v>
+        <v>91</v>
       </c>
       <c r="F354" s="11">
-        <v>97.20930232558139</v>
+        <v>126.9767441860465</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A355" s="6" t="s">
+      <c r="A355" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="B355" s="6" t="s">
-        <v>701</v>
-      </c>
-      <c r="C355" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="D355" s="7">
-        <v>21</v>
+      <c r="B355" s="4"/>
+      <c r="C355" s="4"/>
+      <c r="D355" s="5">
+        <v>20</v>
       </c>
       <c r="E355" s="10">
-        <v>193.66666666666671</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="F355" s="11">
-        <v>270.23255813953489</v>
+        <v>19.767441860465119</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="B356" s="6" t="s">
         <v>702</v>
       </c>
-      <c r="B356" s="6" t="s">
+      <c r="C356" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="C356" s="6" t="s">
-        <v>563</v>
-      </c>
       <c r="D356" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E356" s="10">
-        <v>91</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="F356" s="11">
-        <v>126.9767441860465</v>
+        <v>19.767441860465119</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -10446,13 +10430,13 @@
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
       <c r="D357" s="5">
-        <v>20</v>
+        <v>967</v>
       </c>
       <c r="E357" s="10">
-        <v>14.16666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F357" s="11">
-        <v>19.767441860465119</v>
+        <v>2.3255813953488369</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -10466,13 +10450,13 @@
         <v>707</v>
       </c>
       <c r="D358" s="7">
-        <v>20</v>
+        <v>967</v>
       </c>
       <c r="E358" s="10">
-        <v>14.16666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F358" s="11">
-        <v>19.767441860465119</v>
+        <v>2.3255813953488369</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
@@ -10482,16 +10466,16 @@
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
       <c r="D359" s="5">
-        <v>967</v>
+        <v>402</v>
       </c>
       <c r="E359" s="10">
-        <v>1.666666666666667</v>
+        <v>3494.416666666667</v>
       </c>
       <c r="F359" s="11">
-        <v>2.3255813953488369</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4875.9302325581402</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
         <v>709</v>
       </c>
@@ -10502,52 +10486,56 @@
         <v>711</v>
       </c>
       <c r="D360" s="7">
-        <v>967</v>
+        <v>46</v>
       </c>
       <c r="E360" s="10">
-        <v>1.666666666666667</v>
+        <v>850</v>
       </c>
       <c r="F360" s="11">
-        <v>2.3255813953488369</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A361" s="4" t="s">
+        <v>1186.046511627907</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A361" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="B361" s="4"/>
-      <c r="C361" s="4"/>
-      <c r="D361" s="5">
-        <v>402</v>
+      <c r="B361" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="D361" s="7">
+        <v>18</v>
       </c>
       <c r="E361" s="10">
-        <v>3494.416666666667</v>
+        <v>1041.666666666667</v>
       </c>
       <c r="F361" s="11">
-        <v>4875.9302325581402</v>
+        <v>1453.4883720930229</v>
       </c>
     </row>
     <row r="362" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D362" s="7">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E362" s="10">
-        <v>850</v>
+        <v>941.66666666666674</v>
       </c>
       <c r="F362" s="11">
-        <v>1186.046511627907</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1313.953488372093</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="6" t="s">
         <v>716</v>
       </c>
@@ -10555,19 +10543,19 @@
         <v>717</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D363" s="7">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="E363" s="10">
-        <v>1041.666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F363" s="11">
-        <v>1453.4883720930229</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2.3255813953488369</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="6" t="s">
         <v>718</v>
       </c>
@@ -10575,16 +10563,16 @@
         <v>719</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D364" s="7">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E364" s="10">
-        <v>941.66666666666674</v>
+        <v>20.666666666666671</v>
       </c>
       <c r="F364" s="11">
-        <v>1313.953488372093</v>
+        <v>28.837209302325579</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -10595,16 +10583,16 @@
         <v>721</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D365" s="7">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="E365" s="10">
-        <v>1.666666666666667</v>
+        <v>46.000000000000007</v>
       </c>
       <c r="F365" s="11">
-        <v>2.3255813953488369</v>
+        <v>64.186046511627907</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -10615,16 +10603,16 @@
         <v>723</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D366" s="7">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E366" s="10">
-        <v>20.666666666666671</v>
+        <v>73.5</v>
       </c>
       <c r="F366" s="11">
-        <v>28.837209302325579</v>
+        <v>102.55813953488369</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -10635,92 +10623,92 @@
         <v>725</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D367" s="7">
         <v>23</v>
       </c>
       <c r="E367" s="10">
-        <v>46.000000000000007</v>
+        <v>131</v>
       </c>
       <c r="F367" s="11">
-        <v>64.186046511627907</v>
+        <v>182.7906976744186</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A368" s="6" t="s">
+      <c r="A368" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="B368" s="6" t="s">
-        <v>727</v>
-      </c>
-      <c r="C368" s="6" t="s">
-        <v>715</v>
-      </c>
-      <c r="D368" s="7">
-        <v>29</v>
+      <c r="B368" s="4"/>
+      <c r="C368" s="4"/>
+      <c r="D368" s="5">
+        <v>1057</v>
       </c>
       <c r="E368" s="10">
-        <v>73.5</v>
+        <v>1386.883333333333</v>
       </c>
       <c r="F368" s="11">
-        <v>102.55813953488369</v>
+        <v>1935.1860465116281</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B369" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="B369" s="6" t="s">
+      <c r="C369" s="6" t="s">
         <v>729</v>
       </c>
-      <c r="C369" s="6" t="s">
-        <v>715</v>
-      </c>
       <c r="D369" s="7">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E369" s="10">
-        <v>131</v>
+        <v>5.5833333333333339</v>
       </c>
       <c r="F369" s="11">
-        <v>182.7906976744186</v>
+        <v>7.7906976744186052</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
+      <c r="A370" s="6" t="s">
         <v>730</v>
       </c>
-      <c r="B370" s="4"/>
-      <c r="C370" s="4"/>
-      <c r="D370" s="5">
-        <v>1057</v>
+      <c r="B370" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="D370" s="7">
+        <v>15</v>
       </c>
       <c r="E370" s="10">
-        <v>1386.883333333333</v>
+        <v>6.9166666666666679</v>
       </c>
       <c r="F370" s="11">
-        <v>1935.1860465116281</v>
+        <v>9.6511627906976756</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D371" s="7">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E371" s="10">
-        <v>5.5833333333333339</v>
+        <v>8.8333333333333339</v>
       </c>
       <c r="F371" s="11">
-        <v>7.7906976744186052</v>
+        <v>12.32558139534884</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -10731,16 +10719,16 @@
         <v>735</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D372" s="7">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E372" s="10">
-        <v>6.9166666666666679</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="F372" s="11">
-        <v>9.6511627906976756</v>
+        <v>18.02325581395349</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -10751,16 +10739,16 @@
         <v>737</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D373" s="7">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E373" s="10">
-        <v>8.8333333333333339</v>
+        <v>2.75</v>
       </c>
       <c r="F373" s="11">
-        <v>12.32558139534884</v>
+        <v>3.8372093023255811</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -10771,16 +10759,16 @@
         <v>739</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D374" s="7">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E374" s="10">
-        <v>12.91666666666667</v>
+        <v>4.9333333333333336</v>
       </c>
       <c r="F374" s="11">
-        <v>18.02325581395349</v>
+        <v>6.8837209302325579</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
@@ -10791,16 +10779,16 @@
         <v>741</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D375" s="7">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E375" s="10">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="F375" s="11">
-        <v>3.8372093023255811</v>
+        <v>2.0930232558139541</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -10811,16 +10799,16 @@
         <v>743</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D376" s="7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E376" s="10">
-        <v>4.9333333333333336</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="F376" s="11">
-        <v>6.8837209302325579</v>
+        <v>17.209302325581401</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
@@ -10831,16 +10819,16 @@
         <v>745</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D377" s="7">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E377" s="10">
-        <v>1.5</v>
+        <v>12.41666666666667</v>
       </c>
       <c r="F377" s="11">
-        <v>2.0930232558139541</v>
+        <v>17.325581395348841</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -10851,16 +10839,16 @@
         <v>747</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D378" s="7">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E378" s="10">
-        <v>12.33333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="F378" s="11">
-        <v>17.209302325581401</v>
+        <v>4.5348837209302326</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -10871,16 +10859,16 @@
         <v>749</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D379" s="7">
         <v>15</v>
       </c>
       <c r="E379" s="10">
-        <v>12.41666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="F379" s="11">
-        <v>17.325581395348841</v>
+        <v>4.5348837209302326</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
@@ -10891,7 +10879,7 @@
         <v>751</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D380" s="7">
         <v>35</v>
@@ -10911,16 +10899,16 @@
         <v>753</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D381" s="7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E381" s="10">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="F381" s="11">
-        <v>4.5348837209302326</v>
+        <v>19.534883720930239</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -10931,16 +10919,16 @@
         <v>755</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D382" s="7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E382" s="10">
-        <v>3.25</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="F382" s="11">
-        <v>4.5348837209302326</v>
+        <v>1.86046511627907</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -10951,16 +10939,16 @@
         <v>757</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D383" s="7">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E383" s="10">
-        <v>14</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="F383" s="11">
-        <v>19.534883720930239</v>
+        <v>53.651162790697683</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
@@ -10971,16 +10959,16 @@
         <v>759</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D384" s="7">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E384" s="10">
-        <v>1.333333333333333</v>
+        <v>9.3333333333333357</v>
       </c>
       <c r="F384" s="11">
-        <v>1.86046511627907</v>
+        <v>13.02325581395349</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -10991,16 +10979,16 @@
         <v>761</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D385" s="7">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E385" s="10">
-        <v>38.450000000000003</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="F385" s="11">
-        <v>53.651162790697683</v>
+        <v>58.139534883720927</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -11011,19 +10999,19 @@
         <v>763</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D386" s="7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E386" s="10">
-        <v>9.3333333333333357</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="F386" s="11">
-        <v>13.02325581395349</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+        <v>16.279069767441861</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6" t="s">
         <v>764</v>
       </c>
@@ -11031,16 +11019,16 @@
         <v>765</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D387" s="7">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="E387" s="10">
-        <v>41.666666666666671</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="F387" s="11">
-        <v>58.139534883720927</v>
+        <v>4.6511627906976747</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -11051,19 +11039,19 @@
         <v>767</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D388" s="7">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E388" s="10">
-        <v>11.66666666666667</v>
+        <v>74.833333333333329</v>
       </c>
       <c r="F388" s="11">
-        <v>16.279069767441861</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104.41860465116279</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="6" t="s">
         <v>768</v>
       </c>
@@ -11071,16 +11059,16 @@
         <v>769</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D389" s="7">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="E389" s="10">
-        <v>3.333333333333333</v>
+        <v>93.416666666666671</v>
       </c>
       <c r="F389" s="11">
-        <v>4.6511627906976747</v>
+        <v>130.3488372093023</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -11091,16 +11079,16 @@
         <v>771</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D390" s="7">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E390" s="10">
-        <v>74.833333333333329</v>
+        <v>99.333333333333343</v>
       </c>
       <c r="F390" s="11">
-        <v>104.41860465116279</v>
+        <v>138.6046511627907</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -11111,16 +11099,16 @@
         <v>773</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D391" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E391" s="10">
-        <v>93.416666666666671</v>
+        <v>132.33333333333329</v>
       </c>
       <c r="F391" s="11">
-        <v>130.3488372093023</v>
+        <v>184.6511627906977</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -11131,16 +11119,16 @@
         <v>775</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D392" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E392" s="10">
-        <v>99.333333333333343</v>
+        <v>84.333333333333343</v>
       </c>
       <c r="F392" s="11">
-        <v>138.6046511627907</v>
+        <v>117.67441860465119</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -11151,16 +11139,16 @@
         <v>777</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D393" s="7">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E393" s="10">
-        <v>132.33333333333329</v>
+        <v>47.083333333333343</v>
       </c>
       <c r="F393" s="11">
-        <v>184.6511627906977</v>
+        <v>65.697674418604649</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -11171,16 +11159,16 @@
         <v>779</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D394" s="7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E394" s="10">
-        <v>84.333333333333343</v>
+        <v>58.333333333333343</v>
       </c>
       <c r="F394" s="11">
-        <v>117.67441860465119</v>
+        <v>81.395348837209298</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
@@ -11191,19 +11179,19 @@
         <v>781</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D395" s="7">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E395" s="10">
-        <v>47.083333333333343</v>
+        <v>55.833333333333343</v>
       </c>
       <c r="F395" s="11">
-        <v>65.697674418604649</v>
-      </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+        <v>77.906976744186053</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
         <v>782</v>
       </c>
@@ -11211,16 +11199,16 @@
         <v>783</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D396" s="7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E396" s="10">
-        <v>58.333333333333343</v>
+        <v>20.916666666666671</v>
       </c>
       <c r="F396" s="11">
-        <v>81.395348837209298</v>
+        <v>29.186046511627911</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -11231,92 +11219,92 @@
         <v>785</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D397" s="7">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="E397" s="10">
-        <v>55.833333333333343</v>
+        <v>79</v>
       </c>
       <c r="F397" s="11">
-        <v>77.906976744186053</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="6" t="s">
+        <v>110.2325581395349</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A398" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="B398" s="6" t="s">
-        <v>787</v>
-      </c>
-      <c r="C398" s="6" t="s">
-        <v>733</v>
-      </c>
-      <c r="D398" s="7">
-        <v>23</v>
+      <c r="B398" s="4"/>
+      <c r="C398" s="4"/>
+      <c r="D398" s="5">
+        <v>145</v>
       </c>
       <c r="E398" s="10">
-        <v>20.916666666666671</v>
+        <v>530.58333333333337</v>
       </c>
       <c r="F398" s="11">
-        <v>29.186046511627911</v>
+        <v>740.34883720930236</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="B399" s="6" t="s">
         <v>788</v>
       </c>
-      <c r="B399" s="6" t="s">
+      <c r="C399" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="C399" s="6" t="s">
-        <v>733</v>
-      </c>
       <c r="D399" s="7">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E399" s="10">
-        <v>79</v>
+        <v>25.833333333333339</v>
       </c>
       <c r="F399" s="11">
-        <v>110.2325581395349</v>
+        <v>36.04651162790698</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A400" s="4" t="s">
+      <c r="A400" s="6" t="s">
         <v>790</v>
       </c>
-      <c r="B400" s="4"/>
-      <c r="C400" s="4"/>
-      <c r="D400" s="5">
-        <v>145</v>
+      <c r="B400" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="D400" s="7">
+        <v>42</v>
       </c>
       <c r="E400" s="10">
-        <v>530.58333333333337</v>
+        <v>35.833333333333343</v>
       </c>
       <c r="F400" s="11">
-        <v>740.34883720930236</v>
+        <v>50</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="D401" s="7">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E401" s="10">
-        <v>25.833333333333339</v>
+        <v>48.833333333333343</v>
       </c>
       <c r="F401" s="11">
-        <v>36.04651162790698</v>
+        <v>68.139534883720927</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
@@ -11327,16 +11315,16 @@
         <v>795</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="D402" s="7">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E402" s="10">
-        <v>35.833333333333343</v>
+        <v>44.5</v>
       </c>
       <c r="F402" s="11">
-        <v>50</v>
+        <v>62.093023255813947</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -11347,92 +11335,92 @@
         <v>797</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="D403" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E403" s="10">
-        <v>48.833333333333343</v>
+        <v>31.65</v>
       </c>
       <c r="F403" s="11">
-        <v>68.139534883720927</v>
+        <v>44.162790697674417</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A404" s="6" t="s">
+      <c r="A404" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="B404" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="C404" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="D404" s="7">
-        <v>21</v>
+      <c r="B404" s="4"/>
+      <c r="C404" s="4"/>
+      <c r="D404" s="5">
+        <v>357</v>
       </c>
       <c r="E404" s="10">
-        <v>44.5</v>
+        <v>1270.116666666667</v>
       </c>
       <c r="F404" s="11">
-        <v>62.093023255813947</v>
+        <v>1772.255813953489</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B405" s="6" t="s">
         <v>800</v>
       </c>
-      <c r="B405" s="6" t="s">
+      <c r="C405" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="C405" s="6" t="s">
-        <v>793</v>
-      </c>
       <c r="D405" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E405" s="10">
-        <v>31.65</v>
+        <v>89.166666666666671</v>
       </c>
       <c r="F405" s="11">
-        <v>44.162790697674417</v>
+        <v>124.41860465116279</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A406" s="4" t="s">
+      <c r="A406" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="B406" s="4"/>
-      <c r="C406" s="4"/>
-      <c r="D406" s="5">
-        <v>357</v>
+      <c r="B406" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="C406" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="D406" s="7">
+        <v>20</v>
       </c>
       <c r="E406" s="10">
-        <v>1270.116666666667</v>
+        <v>23.25</v>
       </c>
       <c r="F406" s="11">
-        <v>1772.255813953489</v>
+        <v>32.441860465116278</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D407" s="7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E407" s="10">
-        <v>89.166666666666671</v>
+        <v>25.416666666666671</v>
       </c>
       <c r="F407" s="11">
-        <v>124.41860465116279</v>
+        <v>35.465116279069768</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -11443,16 +11431,16 @@
         <v>807</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D408" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E408" s="10">
-        <v>23.25</v>
+        <v>60.833333333333343</v>
       </c>
       <c r="F408" s="11">
-        <v>32.441860465116278</v>
+        <v>84.883720930232556</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
@@ -11463,16 +11451,16 @@
         <v>809</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D409" s="7">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E409" s="10">
-        <v>25.416666666666671</v>
+        <v>110.8333333333333</v>
       </c>
       <c r="F409" s="11">
-        <v>35.465116279069768</v>
+        <v>154.6511627906977</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -11483,16 +11471,16 @@
         <v>811</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D410" s="7">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E410" s="10">
-        <v>60.833333333333343</v>
+        <v>49.166666666666671</v>
       </c>
       <c r="F410" s="11">
-        <v>84.883720930232556</v>
+        <v>68.604651162790702</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
@@ -11503,16 +11491,16 @@
         <v>813</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D411" s="7">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E411" s="10">
-        <v>110.8333333333333</v>
+        <v>49.916666666666657</v>
       </c>
       <c r="F411" s="11">
-        <v>154.6511627906977</v>
+        <v>69.651162790697668</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
@@ -11523,16 +11511,16 @@
         <v>815</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D412" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E412" s="10">
-        <v>49.166666666666671</v>
+        <v>41.583333333333343</v>
       </c>
       <c r="F412" s="11">
-        <v>68.604651162790702</v>
+        <v>58.02325581395349</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -11543,16 +11531,16 @@
         <v>817</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D413" s="7">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E413" s="10">
-        <v>49.916666666666657</v>
+        <v>12.5</v>
       </c>
       <c r="F413" s="11">
-        <v>69.651162790697668</v>
+        <v>17.441860465116282</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -11563,16 +11551,16 @@
         <v>819</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D414" s="7">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E414" s="10">
-        <v>41.583333333333343</v>
+        <v>8</v>
       </c>
       <c r="F414" s="11">
-        <v>58.02325581395349</v>
+        <v>11.162790697674421</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -11583,16 +11571,16 @@
         <v>821</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D415" s="7">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E415" s="10">
-        <v>12.5</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="F415" s="11">
-        <v>17.441860465116282</v>
+        <v>12.67441860465116</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -11603,16 +11591,16 @@
         <v>823</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D416" s="7">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E416" s="10">
-        <v>8</v>
+        <v>79.916666666666671</v>
       </c>
       <c r="F416" s="11">
-        <v>11.162790697674421</v>
+        <v>111.5116279069768</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
@@ -11623,56 +11611,52 @@
         <v>825</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D417" s="7">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E417" s="10">
-        <v>9.0833333333333339</v>
+        <v>89.166666666666671</v>
       </c>
       <c r="F417" s="11">
-        <v>12.67441860465116</v>
+        <v>124.41860465116279</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A418" s="6" t="s">
+      <c r="A418" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="B418" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="C418" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="D418" s="7">
-        <v>34</v>
+      <c r="B418" s="4"/>
+      <c r="C418" s="4"/>
+      <c r="D418" s="5">
+        <v>180</v>
       </c>
       <c r="E418" s="10">
-        <v>79.916666666666671</v>
+        <v>1651.083333333333</v>
       </c>
       <c r="F418" s="11">
-        <v>111.5116279069768</v>
+        <v>2303.8372093023258</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B419" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="B419" s="6" t="s">
+      <c r="C419" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="C419" s="6" t="s">
-        <v>805</v>
-      </c>
       <c r="D419" s="7">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E419" s="10">
-        <v>89.166666666666671</v>
+        <v>70</v>
       </c>
       <c r="F419" s="11">
-        <v>124.41860465116279</v>
+        <v>97.674418604651166</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -11682,13 +11666,13 @@
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
       <c r="D420" s="5">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="E420" s="10">
-        <v>1651.083333333333</v>
+        <v>6934.666666666667</v>
       </c>
       <c r="F420" s="11">
-        <v>2303.8372093023258</v>
+        <v>9676.2790697674427</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -11702,105 +11686,109 @@
         <v>833</v>
       </c>
       <c r="D421" s="7">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="E421" s="10">
-        <v>70</v>
+        <v>27.5</v>
       </c>
       <c r="F421" s="11">
-        <v>97.674418604651166</v>
+        <v>38.372093023255808</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A422" s="4" t="s">
+      <c r="A422" s="6" t="s">
         <v>834</v>
       </c>
-      <c r="B422" s="4"/>
-      <c r="C422" s="4"/>
-      <c r="D422" s="5">
-        <v>63</v>
+      <c r="B422" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="D422" s="7">
+        <v>17</v>
       </c>
       <c r="E422" s="10">
-        <v>6934.666666666667</v>
+        <v>54.166666666666671</v>
       </c>
       <c r="F422" s="11">
-        <v>9676.2790697674427</v>
+        <v>75.581395348837205</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A423" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="B423" s="6" t="s">
+      <c r="A423" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="C423" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="D423" s="7">
-        <v>38</v>
+      <c r="B423" s="4"/>
+      <c r="C423" s="4"/>
+      <c r="D423" s="5">
+        <v>1556</v>
       </c>
       <c r="E423" s="10">
-        <v>27.5</v>
+        <v>1972.583333333333</v>
       </c>
       <c r="F423" s="11">
-        <v>38.372093023255808</v>
+        <v>2752.441860465116</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="B424" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="B424" s="6" t="s">
+      <c r="C424" s="6" t="s">
         <v>839</v>
       </c>
-      <c r="C424" s="6" t="s">
-        <v>837</v>
-      </c>
       <c r="D424" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E424" s="10">
-        <v>54.166666666666671</v>
+        <v>26.166666666666671</v>
       </c>
       <c r="F424" s="11">
-        <v>75.581395348837205</v>
+        <v>36.511627906976742</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A425" s="4" t="s">
+      <c r="A425" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="B425" s="4"/>
-      <c r="C425" s="4"/>
-      <c r="D425" s="5">
-        <v>1556</v>
+      <c r="B425" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="C425" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="D425" s="7">
+        <v>30</v>
       </c>
       <c r="E425" s="10">
-        <v>1972.583333333333</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="F425" s="11">
-        <v>2752.441860465116</v>
+        <v>78.139534883720941</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D426" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E426" s="10">
-        <v>26.166666666666671</v>
+        <v>43.25</v>
       </c>
       <c r="F426" s="11">
-        <v>36.511627906976742</v>
+        <v>60.348837209302317</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -11811,16 +11799,16 @@
         <v>845</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D427" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E427" s="10">
-        <v>56.000000000000007</v>
+        <v>51.000000000000007</v>
       </c>
       <c r="F427" s="11">
-        <v>78.139534883720941</v>
+        <v>71.162790697674424</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -11831,16 +11819,16 @@
         <v>847</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D428" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E428" s="10">
-        <v>43.25</v>
+        <v>24.916666666666671</v>
       </c>
       <c r="F428" s="11">
-        <v>60.348837209302317</v>
+        <v>34.767441860465112</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -11851,16 +11839,16 @@
         <v>849</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D429" s="7">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E429" s="10">
-        <v>51.000000000000007</v>
+        <v>28.5</v>
       </c>
       <c r="F429" s="11">
-        <v>71.162790697674424</v>
+        <v>39.767441860465119</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -11871,16 +11859,16 @@
         <v>851</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D430" s="7">
         <v>20</v>
       </c>
       <c r="E430" s="10">
-        <v>24.916666666666671</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="F430" s="11">
-        <v>34.767441860465112</v>
+        <v>12.67441860465116</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -11891,16 +11879,16 @@
         <v>853</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D431" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E431" s="10">
-        <v>28.5</v>
+        <v>9.1666666666666679</v>
       </c>
       <c r="F431" s="11">
-        <v>39.767441860465119</v>
+        <v>12.790697674418601</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -11911,16 +11899,16 @@
         <v>855</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D432" s="7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E432" s="10">
-        <v>9.0833333333333339</v>
+        <v>8</v>
       </c>
       <c r="F432" s="11">
-        <v>12.67441860465116</v>
+        <v>11.162790697674421</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
@@ -11931,16 +11919,16 @@
         <v>857</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D433" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E433" s="10">
-        <v>9.1666666666666679</v>
+        <v>57.333333333333343</v>
       </c>
       <c r="F433" s="11">
-        <v>12.790697674418601</v>
+        <v>80</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -11951,16 +11939,16 @@
         <v>859</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D434" s="7">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E434" s="10">
-        <v>8</v>
+        <v>35.166666666666671</v>
       </c>
       <c r="F434" s="11">
-        <v>11.162790697674421</v>
+        <v>49.069767441860471</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -11971,16 +11959,16 @@
         <v>861</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D435" s="7">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E435" s="10">
-        <v>57.333333333333343</v>
+        <v>10.5</v>
       </c>
       <c r="F435" s="11">
-        <v>80</v>
+        <v>14.65116279069767</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -11991,16 +11979,16 @@
         <v>863</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D436" s="7">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="E436" s="10">
-        <v>35.166666666666671</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="F436" s="11">
-        <v>49.069767441860471</v>
+        <v>14.53488372093023</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
@@ -12011,16 +11999,16 @@
         <v>865</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D437" s="7">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="E437" s="10">
-        <v>10.5</v>
+        <v>17.666666666666671</v>
       </c>
       <c r="F437" s="11">
-        <v>14.65116279069767</v>
+        <v>24.651162790697679</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
@@ -12031,16 +12019,16 @@
         <v>867</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D438" s="7">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E438" s="10">
-        <v>10.41666666666667</v>
+        <v>17.833333333333329</v>
       </c>
       <c r="F438" s="11">
-        <v>14.53488372093023</v>
+        <v>24.88372093023256</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -12051,16 +12039,16 @@
         <v>869</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D439" s="7">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="E439" s="10">
-        <v>17.666666666666671</v>
+        <v>59</v>
       </c>
       <c r="F439" s="11">
-        <v>24.651162790697679</v>
+        <v>82.325581395348834</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -12071,16 +12059,16 @@
         <v>871</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D440" s="7">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E440" s="10">
-        <v>17.833333333333329</v>
+        <v>73</v>
       </c>
       <c r="F440" s="11">
-        <v>24.88372093023256</v>
+        <v>101.8604651162791</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
@@ -12091,16 +12079,16 @@
         <v>873</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D441" s="7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E441" s="10">
-        <v>59</v>
+        <v>26.583333333333329</v>
       </c>
       <c r="F441" s="11">
-        <v>82.325581395348834</v>
+        <v>37.093023255813947</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
@@ -12111,16 +12099,16 @@
         <v>875</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D442" s="7">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E442" s="10">
-        <v>73</v>
+        <v>91.083333333333329</v>
       </c>
       <c r="F442" s="11">
-        <v>101.8604651162791</v>
+        <v>127.0930232558139</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -12131,16 +12119,16 @@
         <v>877</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D443" s="7">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E443" s="10">
-        <v>26.583333333333329</v>
+        <v>57.083333333333343</v>
       </c>
       <c r="F443" s="11">
-        <v>37.093023255813947</v>
+        <v>79.651162790697683</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -12151,16 +12139,16 @@
         <v>879</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D444" s="7">
         <v>15</v>
       </c>
       <c r="E444" s="10">
-        <v>91.083333333333329</v>
+        <v>86.25</v>
       </c>
       <c r="F444" s="11">
-        <v>127.0930232558139</v>
+        <v>120.3488372093023</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -12171,16 +12159,16 @@
         <v>881</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D445" s="7">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E445" s="10">
-        <v>57.083333333333343</v>
+        <v>83.250000000000014</v>
       </c>
       <c r="F445" s="11">
-        <v>79.651162790697683</v>
+        <v>116.1627906976744</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -12191,16 +12179,16 @@
         <v>883</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D446" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E446" s="10">
-        <v>86.25</v>
+        <v>81.333333333333329</v>
       </c>
       <c r="F446" s="11">
-        <v>120.3488372093023</v>
+        <v>113.4883720930232</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -12211,16 +12199,16 @@
         <v>885</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D447" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E447" s="10">
-        <v>83.250000000000014</v>
+        <v>83.75</v>
       </c>
       <c r="F447" s="11">
-        <v>116.1627906976744</v>
+        <v>116.8604651162791</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
@@ -12231,16 +12219,16 @@
         <v>887</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D448" s="7">
-        <v>12</v>
+        <v>406</v>
       </c>
       <c r="E448" s="10">
-        <v>81.333333333333329</v>
+        <v>38.75</v>
       </c>
       <c r="F448" s="11">
-        <v>113.4883720930232</v>
+        <v>54.069767441860463</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
@@ -12251,16 +12239,16 @@
         <v>889</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D449" s="7">
-        <v>15</v>
+        <v>311</v>
       </c>
       <c r="E449" s="10">
-        <v>83.75</v>
+        <v>26.583333333333329</v>
       </c>
       <c r="F449" s="11">
-        <v>116.8604651162791</v>
+        <v>37.093023255813947</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
@@ -12271,10 +12259,10 @@
         <v>891</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D450" s="7">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="E450" s="10">
         <v>38.75</v>
@@ -12291,56 +12279,52 @@
         <v>893</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D451" s="7">
-        <v>311</v>
+        <v>14</v>
       </c>
       <c r="E451" s="10">
-        <v>26.583333333333329</v>
+        <v>74.500000000000014</v>
       </c>
       <c r="F451" s="11">
-        <v>37.093023255813947</v>
+        <v>103.95348837209301</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A452" s="6" t="s">
+      <c r="A452" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="B452" s="6" t="s">
-        <v>895</v>
-      </c>
-      <c r="C452" s="6" t="s">
-        <v>843</v>
-      </c>
-      <c r="D452" s="7">
-        <v>20</v>
+      <c r="B452" s="4"/>
+      <c r="C452" s="4"/>
+      <c r="D452" s="5">
+        <v>19</v>
       </c>
       <c r="E452" s="10">
-        <v>38.75</v>
+        <v>43.25</v>
       </c>
       <c r="F452" s="11">
-        <v>54.069767441860463</v>
+        <v>60.348837209302317</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="B453" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="B453" s="6" t="s">
+      <c r="C453" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="C453" s="6" t="s">
-        <v>843</v>
-      </c>
       <c r="D453" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E453" s="10">
-        <v>74.500000000000014</v>
+        <v>43.25</v>
       </c>
       <c r="F453" s="11">
-        <v>103.95348837209301</v>
+        <v>60.348837209302317</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.3">
@@ -12350,13 +12334,13 @@
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
       <c r="D454" s="5">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="E454" s="10">
-        <v>43.25</v>
+        <v>302.5</v>
       </c>
       <c r="F454" s="11">
-        <v>60.348837209302317</v>
+        <v>422.09302325581388</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
@@ -12370,105 +12354,109 @@
         <v>901</v>
       </c>
       <c r="D455" s="7">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E455" s="10">
-        <v>43.25</v>
+        <v>151.25</v>
       </c>
       <c r="F455" s="11">
-        <v>60.348837209302317</v>
+        <v>211.04651162790699</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A456" s="4" t="s">
+      <c r="A456" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="B456" s="4"/>
-      <c r="C456" s="4"/>
-      <c r="D456" s="5">
-        <v>100</v>
+      <c r="B456" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="D456" s="7">
+        <v>57</v>
       </c>
       <c r="E456" s="10">
-        <v>302.5</v>
+        <v>151.25</v>
       </c>
       <c r="F456" s="11">
-        <v>422.09302325581388</v>
+        <v>211.04651162790699</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A457" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="B457" s="6" t="s">
+      <c r="A457" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C457" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="D457" s="7">
-        <v>43</v>
+      <c r="B457" s="4"/>
+      <c r="C457" s="4"/>
+      <c r="D457" s="5">
+        <v>383</v>
       </c>
       <c r="E457" s="10">
-        <v>151.25</v>
+        <v>454.41666666666657</v>
       </c>
       <c r="F457" s="11">
-        <v>211.04651162790699</v>
+        <v>634.06976744186045</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="B458" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="B458" s="6" t="s">
+      <c r="C458" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="C458" s="6" t="s">
-        <v>905</v>
-      </c>
       <c r="D458" s="7">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E458" s="10">
-        <v>151.25</v>
+        <v>75</v>
       </c>
       <c r="F458" s="11">
-        <v>211.04651162790699</v>
+        <v>104.6511627906977</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="B459" s="4"/>
-      <c r="C459" s="4"/>
-      <c r="D459" s="5">
-        <v>383</v>
+      <c r="B459" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="C459" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="D459" s="7">
+        <v>100</v>
       </c>
       <c r="E459" s="10">
-        <v>454.41666666666657</v>
+        <v>30</v>
       </c>
       <c r="F459" s="11">
-        <v>634.06976744186045</v>
+        <v>41.860465116279073</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D460" s="7">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="E460" s="10">
-        <v>75</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="F460" s="11">
-        <v>104.6511627906977</v>
+        <v>18.604651162790699</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.3">
@@ -12479,16 +12467,16 @@
         <v>913</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D461" s="7">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E461" s="10">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F461" s="11">
-        <v>41.860465116279073</v>
+        <v>111.6279069767442</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.3">
@@ -12499,56 +12487,52 @@
         <v>915</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D462" s="7">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="E462" s="10">
-        <v>13.33333333333333</v>
+        <v>42.75</v>
       </c>
       <c r="F462" s="11">
-        <v>18.604651162790699</v>
+        <v>59.651162790697683</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A463" s="6" t="s">
+      <c r="A463" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="B463" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="C463" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="D463" s="7">
+      <c r="B463" s="4"/>
+      <c r="C463" s="4"/>
+      <c r="D463" s="5">
         <v>32</v>
       </c>
       <c r="E463" s="10">
-        <v>80</v>
+        <v>255.66666666666671</v>
       </c>
       <c r="F463" s="11">
-        <v>111.6279069767442</v>
+        <v>356.74418604651157</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="B464" s="6" t="s">
         <v>918</v>
       </c>
-      <c r="B464" s="6" t="s">
+      <c r="C464" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="C464" s="6" t="s">
-        <v>911</v>
-      </c>
       <c r="D464" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E464" s="10">
-        <v>42.75</v>
+        <v>48.25</v>
       </c>
       <c r="F464" s="11">
-        <v>59.651162790697683</v>
+        <v>67.325581395348834</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
@@ -12558,13 +12542,13 @@
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
       <c r="D465" s="5">
-        <v>32</v>
+        <v>2396</v>
       </c>
       <c r="E465" s="10">
-        <v>255.66666666666671</v>
+        <v>1049.3166666666671</v>
       </c>
       <c r="F465" s="11">
-        <v>356.74418604651157</v>
+        <v>1464.1627906976751</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
@@ -12578,49 +12562,53 @@
         <v>923</v>
       </c>
       <c r="D466" s="7">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E466" s="10">
-        <v>48.25</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="F466" s="11">
-        <v>67.325581395348834</v>
+        <v>5.3488372093023253</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="B467" s="4"/>
-      <c r="C467" s="4"/>
-      <c r="D467" s="5">
-        <v>2396</v>
+      <c r="B467" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="C467" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="D467" s="7">
+        <v>23</v>
       </c>
       <c r="E467" s="10">
-        <v>1049.3166666666671</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="F467" s="11">
-        <v>1464.1627906976751</v>
+        <v>5.8139534883720927</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D468" s="7">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E468" s="10">
-        <v>3.833333333333333</v>
+        <v>18.166666666666671</v>
       </c>
       <c r="F468" s="11">
-        <v>5.3488372093023253</v>
+        <v>25.348837209302332</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
@@ -12631,16 +12619,16 @@
         <v>929</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D469" s="7">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E469" s="10">
-        <v>4.166666666666667</v>
+        <v>11.58333333333333</v>
       </c>
       <c r="F469" s="11">
-        <v>5.8139534883720927</v>
+        <v>16.162790697674421</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
@@ -12651,16 +12639,16 @@
         <v>931</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D470" s="7">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E470" s="10">
-        <v>18.166666666666671</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="F470" s="11">
-        <v>25.348837209302332</v>
+        <v>19.767441860465119</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
@@ -12671,16 +12659,16 @@
         <v>933</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D471" s="7">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E471" s="10">
-        <v>11.58333333333333</v>
+        <v>8.25</v>
       </c>
       <c r="F471" s="11">
-        <v>16.162790697674421</v>
+        <v>11.51162790697675</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
@@ -12691,16 +12679,16 @@
         <v>935</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D472" s="7">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E472" s="10">
-        <v>14.16666666666667</v>
+        <v>27.5</v>
       </c>
       <c r="F472" s="11">
-        <v>19.767441860465119</v>
+        <v>38.372093023255808</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
@@ -12711,16 +12699,16 @@
         <v>937</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D473" s="7">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E473" s="10">
-        <v>8.25</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F473" s="11">
-        <v>11.51162790697675</v>
+        <v>7.558139534883721</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
@@ -12731,16 +12719,16 @@
         <v>939</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D474" s="7">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="E474" s="10">
-        <v>27.5</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="F474" s="11">
-        <v>38.372093023255808</v>
+        <v>2.2093023255813962</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
@@ -12751,16 +12739,16 @@
         <v>941</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D475" s="7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E475" s="10">
-        <v>5.416666666666667</v>
+        <v>13.25</v>
       </c>
       <c r="F475" s="11">
-        <v>7.558139534883721</v>
+        <v>18.488372093023251</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
@@ -12771,16 +12759,16 @@
         <v>943</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D476" s="7">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E476" s="10">
-        <v>1.583333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="F476" s="11">
-        <v>2.2093023255813962</v>
+        <v>1.7441860465116279</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
@@ -12791,16 +12779,16 @@
         <v>945</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D477" s="7">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="E477" s="10">
-        <v>13.25</v>
+        <v>1.25</v>
       </c>
       <c r="F477" s="11">
-        <v>18.488372093023251</v>
+        <v>1.7441860465116279</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
@@ -12811,16 +12799,16 @@
         <v>947</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D478" s="7">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="E478" s="10">
-        <v>1.25</v>
+        <v>26</v>
       </c>
       <c r="F478" s="11">
-        <v>1.7441860465116279</v>
+        <v>36.279069767441861</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
@@ -12831,16 +12819,16 @@
         <v>949</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D479" s="7">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="E479" s="10">
-        <v>1.25</v>
+        <v>20.833333333333339</v>
       </c>
       <c r="F479" s="11">
-        <v>1.7441860465116279</v>
+        <v>29.069767441860471</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
@@ -12851,16 +12839,16 @@
         <v>951</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D480" s="7">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="E480" s="10">
-        <v>26</v>
+        <v>3.75</v>
       </c>
       <c r="F480" s="11">
-        <v>36.279069767441861</v>
+        <v>5.2325581395348841</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
@@ -12871,16 +12859,16 @@
         <v>953</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D481" s="7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E481" s="10">
-        <v>20.833333333333339</v>
+        <v>9.5</v>
       </c>
       <c r="F481" s="11">
-        <v>29.069767441860471</v>
+        <v>13.255813953488371</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
@@ -12891,16 +12879,16 @@
         <v>955</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D482" s="7">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="E482" s="10">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
       <c r="F482" s="11">
-        <v>5.2325581395348841</v>
+        <v>12.209302325581399</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.3">
@@ -12911,16 +12899,16 @@
         <v>957</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D483" s="7">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E483" s="10">
-        <v>9.5</v>
+        <v>26</v>
       </c>
       <c r="F483" s="11">
-        <v>13.255813953488371</v>
+        <v>36.279069767441861</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
@@ -12931,16 +12919,16 @@
         <v>959</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D484" s="7">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="E484" s="10">
-        <v>8.75</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="F484" s="11">
-        <v>12.209302325581399</v>
+        <v>22.09302325581395</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
@@ -12951,16 +12939,16 @@
         <v>961</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D485" s="7">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E485" s="10">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="F485" s="11">
-        <v>36.279069767441861</v>
+        <v>31.395348837209301</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
@@ -12971,16 +12959,16 @@
         <v>963</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D486" s="7">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="E486" s="10">
-        <v>15.83333333333333</v>
+        <v>17.083333333333339</v>
       </c>
       <c r="F486" s="11">
-        <v>22.09302325581395</v>
+        <v>23.837209302325579</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
@@ -12991,16 +12979,16 @@
         <v>965</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D487" s="7">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E487" s="10">
-        <v>22.5</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="F487" s="11">
-        <v>31.395348837209301</v>
+        <v>11.04651162790698</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
@@ -13011,16 +12999,16 @@
         <v>967</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D488" s="7">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="E488" s="10">
-        <v>17.083333333333339</v>
+        <v>33.25</v>
       </c>
       <c r="F488" s="11">
-        <v>23.837209302325579</v>
+        <v>46.395348837209298</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.3">
@@ -13031,16 +13019,16 @@
         <v>969</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D489" s="7">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E489" s="10">
-        <v>7.916666666666667</v>
+        <v>26</v>
       </c>
       <c r="F489" s="11">
-        <v>11.04651162790698</v>
+        <v>36.279069767441861</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
@@ -13051,16 +13039,16 @@
         <v>971</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D490" s="7">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E490" s="10">
-        <v>33.25</v>
+        <v>3</v>
       </c>
       <c r="F490" s="11">
-        <v>46.395348837209298</v>
+        <v>4.1860465116279073</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
@@ -13071,16 +13059,16 @@
         <v>973</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D491" s="7">
         <v>14</v>
       </c>
       <c r="E491" s="10">
-        <v>26</v>
+        <v>27.083333333333339</v>
       </c>
       <c r="F491" s="11">
-        <v>36.279069767441861</v>
+        <v>37.790697674418603</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
@@ -13091,16 +13079,16 @@
         <v>975</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D492" s="7">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E492" s="10">
-        <v>3</v>
+        <v>27.083333333333339</v>
       </c>
       <c r="F492" s="11">
-        <v>4.1860465116279073</v>
+        <v>37.790697674418603</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
@@ -13111,16 +13099,16 @@
         <v>977</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D493" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E493" s="10">
-        <v>27.083333333333339</v>
+        <v>22.833333333333329</v>
       </c>
       <c r="F493" s="11">
-        <v>37.790697674418603</v>
+        <v>31.86046511627907</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
@@ -13131,16 +13119,16 @@
         <v>979</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D494" s="7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E494" s="10">
-        <v>27.083333333333339</v>
+        <v>35.416666666666671</v>
       </c>
       <c r="F494" s="11">
-        <v>37.790697674418603</v>
+        <v>49.418604651162788</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.3">
@@ -13151,16 +13139,16 @@
         <v>981</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D495" s="7">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E495" s="10">
-        <v>22.833333333333329</v>
+        <v>5.916666666666667</v>
       </c>
       <c r="F495" s="11">
-        <v>31.86046511627907</v>
+        <v>8.2558139534883725</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
@@ -13171,16 +13159,16 @@
         <v>983</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D496" s="7">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E496" s="10">
-        <v>35.416666666666671</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F496" s="11">
-        <v>49.418604651162788</v>
+        <v>6.8604651162790704</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
@@ -13191,16 +13179,16 @@
         <v>985</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D497" s="7">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E497" s="10">
-        <v>5.916666666666667</v>
+        <v>13.75</v>
       </c>
       <c r="F497" s="11">
-        <v>8.2558139534883725</v>
+        <v>19.186046511627911</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
@@ -13211,16 +13199,16 @@
         <v>987</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D498" s="7">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E498" s="10">
-        <v>4.916666666666667</v>
+        <v>21.25</v>
       </c>
       <c r="F498" s="11">
-        <v>6.8604651162790704</v>
+        <v>29.651162790697679</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
@@ -13231,16 +13219,16 @@
         <v>989</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D499" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E499" s="10">
-        <v>13.75</v>
+        <v>21.416666666666671</v>
       </c>
       <c r="F499" s="11">
-        <v>19.186046511627911</v>
+        <v>29.88372093023256</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.3">
@@ -13251,112 +13239,72 @@
         <v>991</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D500" s="7">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E500" s="10">
-        <v>21.25</v>
+        <v>22.833333333333329</v>
       </c>
       <c r="F500" s="11">
-        <v>29.651162790697679</v>
+        <v>31.86046511627907</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A501" s="6" t="s">
+      <c r="A501" s="4" t="s">
         <v>992</v>
       </c>
-      <c r="B501" s="6" t="s">
-        <v>993</v>
-      </c>
-      <c r="C501" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="D501" s="7">
-        <v>24</v>
+      <c r="B501" s="4"/>
+      <c r="C501" s="4"/>
+      <c r="D501" s="5">
+        <v>61</v>
       </c>
       <c r="E501" s="10">
-        <v>21.416666666666671</v>
+        <v>102.5</v>
       </c>
       <c r="F501" s="11">
-        <v>29.88372093023256</v>
+        <v>143.02325581395351</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="B502" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="B502" s="6" t="s">
+      <c r="C502" s="6"/>
+      <c r="D502" s="7">
+        <v>42</v>
+      </c>
+      <c r="E502" s="10">
+        <v>77.5</v>
+      </c>
+      <c r="F502" s="11">
+        <v>108.1395348837209</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A503" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="C502" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="D502" s="7">
-        <v>13</v>
-      </c>
-      <c r="E502" s="10">
-        <v>22.833333333333329</v>
-      </c>
-      <c r="F502" s="11">
-        <v>31.86046511627907</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A503" s="4" t="s">
+      <c r="B503" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="B503" s="4"/>
-      <c r="C503" s="4"/>
-      <c r="D503" s="5">
-        <v>61</v>
+      <c r="C503" s="6"/>
+      <c r="D503" s="7">
+        <v>19</v>
       </c>
       <c r="E503" s="10">
-        <v>102.5</v>
+        <v>25</v>
       </c>
       <c r="F503" s="11">
-        <v>143.02325581395351</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A504" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="B504" s="6" t="s">
-        <v>998</v>
-      </c>
-      <c r="C504" s="6"/>
-      <c r="D504" s="7">
-        <v>42</v>
-      </c>
-      <c r="E504" s="10">
-        <v>77.5</v>
-      </c>
-      <c r="F504" s="11">
-        <v>108.1395348837209</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A505" s="6" t="s">
-        <v>999</v>
-      </c>
-      <c r="B505" s="6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C505" s="6"/>
-      <c r="D505" s="7">
-        <v>19</v>
-      </c>
-      <c r="E505" s="10">
-        <v>25</v>
-      </c>
-      <c r="F505" s="11">
         <v>34.883720930232563</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:D505" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A6:D503" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>